--- a/Donnees/Statistiques Démographiques et sociales/Démographie/Demographique_Portail.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Démographie/Demographique_Portail.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Démographie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C14C19-B281-4E3D-8A10-CEBB09518702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1430973-F411-46FC-8EE1-76767237B3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="512" activeTab="4" xr2:uid="{AB8ECA8C-A6C4-4626-BABF-82DEB90B841C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="512" activeTab="7" xr2:uid="{AB8ECA8C-A6C4-4626-BABF-82DEB90B841C}"/>
   </bookViews>
   <sheets>
     <sheet name="T1.1" sheetId="1" r:id="rId1"/>
@@ -36,17 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="120">
   <si>
     <t>Mauritanie</t>
   </si>
   <si>
-    <t>Ensemble Rural</t>
-  </si>
-  <si>
-    <t>Ensemble Urbain</t>
-  </si>
-  <si>
     <t>Nouakchott</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>Groupe d'âge</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t xml:space="preserve">60,3 </t>
   </si>
   <si>
@@ -194,24 +185,9 @@
     <t>Dakhlet Nouadhibou</t>
   </si>
   <si>
-    <t>Population urbaine~Masculine</t>
-  </si>
-  <si>
-    <t>Population urbaine~Féminine</t>
-  </si>
-  <si>
-    <t>Population Rurale/nomade~Masculine</t>
-  </si>
-  <si>
-    <t>Population Rurale/nomade~Féminine</t>
-  </si>
-  <si>
     <t>Fécondité~Indice Synthétique de Fécondité (ISF)</t>
   </si>
   <si>
-    <t>Population (en %)~0 à 4 ans</t>
-  </si>
-  <si>
     <t xml:space="preserve">2000~Filles   </t>
   </si>
   <si>
@@ -239,13 +215,7 @@
     <t xml:space="preserve">                               Total</t>
   </si>
   <si>
-    <t>Tiris Zemmour</t>
-  </si>
-  <si>
     <t>Tableau 1.1: Répartition de la population selon le milieu de résidence et le sexe; 1977 - 2027</t>
-  </si>
-  <si>
-    <t>Hodh Chargui</t>
   </si>
   <si>
     <t>Guidimakha</t>
@@ -287,18 +257,6 @@
     <t xml:space="preserve">2023~Ensemble  </t>
   </si>
   <si>
-    <t>Fécondité~Taux d'accroissement intercensitaire (en %)</t>
-  </si>
-  <si>
-    <t>Population Mauritanie~Masculine</t>
-  </si>
-  <si>
-    <t>Population Mauritanie~Féminine</t>
-  </si>
-  <si>
-    <t>Ensemble Mauritanie</t>
-  </si>
-  <si>
     <t>Tableau 1.4 : Evolution du quotient de mortalité dans l’enfance selon le sexe (en ‰), 2000 - 2023</t>
   </si>
   <si>
@@ -311,9 +269,6 @@
     <t>15-64 ans</t>
   </si>
   <si>
-    <t xml:space="preserve">Fécondité </t>
-  </si>
-  <si>
     <t xml:space="preserve">2019~Garçons  </t>
   </si>
   <si>
@@ -332,33 +287,9 @@
     <t>Tableau 1.7: Répartition de la population par grands groupes d'âge selon le sexe, en 2023</t>
   </si>
   <si>
-    <t>Tableau 1.8 : Principales caractéristiques démographiques de la population; 1977 - 2023</t>
-  </si>
-  <si>
     <t>Tableau 1.9 : Evolution de l'Indice synthétique de fécondité par Wilaya; 2000 - 2023</t>
   </si>
   <si>
-    <t>Population (en %)~6 - 11 ans</t>
-  </si>
-  <si>
-    <t>Population (en %)~12 - 24 ans</t>
-  </si>
-  <si>
-    <t>Population (en %)~ 0 à14 ans</t>
-  </si>
-  <si>
-    <t>Population (en %)~15 à 24 ans</t>
-  </si>
-  <si>
-    <t>Population (en %)~15 à59 ans</t>
-  </si>
-  <si>
-    <t>Population (en %)~65 ans et plus</t>
-  </si>
-  <si>
-    <t>Population (en %)~Femmes 15 à 49 ans</t>
-  </si>
-  <si>
     <t>Source : ANSADE, RGPH 1977-2023 et Projections démographiques 2024</t>
   </si>
   <si>
@@ -368,10 +299,112 @@
     <t xml:space="preserve">Source : ANSADE, RGPH 2023 </t>
   </si>
   <si>
-    <t>Source : ANSADE, RGPH 1977-2023, MICS5 2015 et EDSM 2019-21</t>
-  </si>
-  <si>
     <t>Tableau 1.5: Répartition(en %) de la population par groupe d'âge selon le sexe, en 2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.8 : Principales caractéristiques démographiques de la population; 1977  2023</t>
+  </si>
+  <si>
+    <t>Source : ANSADE, RGPH 19772023, MICS5 2015 et EDSM 201921</t>
+  </si>
+  <si>
+    <t>Mauritanie~Masculine</t>
+  </si>
+  <si>
+    <t>Mauritanie~Féminine</t>
+  </si>
+  <si>
+    <t>Urbain</t>
+  </si>
+  <si>
+    <t>Urbain~Masculine</t>
+  </si>
+  <si>
+    <t>Urbain~Féminine</t>
+  </si>
+  <si>
+    <t>Rural</t>
+  </si>
+  <si>
+    <t>Wilaya~Hodh Chargui</t>
+  </si>
+  <si>
+    <t>Wilaya~Hodh El Gharbi</t>
+  </si>
+  <si>
+    <t>Wilaya~Assaba</t>
+  </si>
+  <si>
+    <t>Wilaya~Gorgol</t>
+  </si>
+  <si>
+    <t>Wilaya~Brakna</t>
+  </si>
+  <si>
+    <t>Wilaya~Trarza</t>
+  </si>
+  <si>
+    <t>Wilaya~Adrar</t>
+  </si>
+  <si>
+    <t>Wilaya~Dakhlet Nouadhibou</t>
+  </si>
+  <si>
+    <t>Wilaya~Tagant</t>
+  </si>
+  <si>
+    <t>Wilaya~Guidimakha</t>
+  </si>
+  <si>
+    <t>Wilaya~Tiris Zemmour</t>
+  </si>
+  <si>
+    <t>Wilaya~Inchiri</t>
+  </si>
+  <si>
+    <t>Wilaya~Nouakchott</t>
+  </si>
+  <si>
+    <t>Wilaya~Nouakchott-Ouest</t>
+  </si>
+  <si>
+    <t>Wilaya~Nouakchott-Nord</t>
+  </si>
+  <si>
+    <t>Wilaya~Nouakchott-Sud</t>
+  </si>
+  <si>
+    <t>Accroissement de la population~Taux d'accroissement intercensitaire (en %)</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~0 à 4 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~6  11 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~12  24 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~ 0 à14 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~15 à 24 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~15 à59 ans</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~65 ans et plus</t>
+  </si>
+  <si>
+    <t>Population des groupes spécifiques(en%)~Femmes 15 à 49 ans</t>
+  </si>
+  <si>
+    <t>Rural~Masculine</t>
+  </si>
+  <si>
+    <t>Rural~Féminine</t>
   </si>
 </sst>
 </file>
@@ -512,7 +545,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -583,13 +616,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -682,27 +743,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -813,6 +859,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1344,18 +1402,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.85">
-      <c r="A1" s="86" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="86"/>
-      <c r="C1" s="86"/>
-      <c r="D1" s="86"/>
-      <c r="E1" s="86"/>
-      <c r="F1" s="86"/>
-      <c r="G1" s="86"/>
-      <c r="H1" s="86"/>
-      <c r="I1" s="86"/>
-      <c r="J1" s="86"/>
+      <c r="A1" s="85" t="s">
+        <v>59</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
+      <c r="H1" s="85"/>
+      <c r="I1" s="85"/>
+      <c r="J1" s="85"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A2" s="10"/>
@@ -1374,22 +1432,22 @@
       <c r="F2" s="8">
         <v>2023</v>
       </c>
-      <c r="G2" s="57">
+      <c r="G2" s="52">
         <v>2024</v>
       </c>
-      <c r="H2" s="57">
+      <c r="H2" s="52">
         <v>2025</v>
       </c>
-      <c r="I2" s="57">
+      <c r="I2" s="52">
         <v>2026</v>
       </c>
-      <c r="J2" s="57">
+      <c r="J2" s="52">
         <v>2027</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A3" s="4" t="s">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3">
         <f>B4+B5</f>
@@ -1410,22 +1468,22 @@
       <c r="F3" s="3">
         <v>4927532</v>
       </c>
-      <c r="G3" s="59">
+      <c r="G3" s="54">
         <v>5020364</v>
       </c>
-      <c r="H3" s="59">
+      <c r="H3" s="54">
         <v>5179819</v>
       </c>
-      <c r="I3" s="59">
+      <c r="I3" s="54">
         <v>5343892</v>
       </c>
-      <c r="J3" s="59">
+      <c r="J3" s="54">
         <v>5512557</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="B4" s="5">
         <f>B7+B10</f>
@@ -1447,26 +1505,26 @@
         <f t="shared" si="1"/>
         <v>2375470</v>
       </c>
-      <c r="G4" s="58">
+      <c r="G4" s="53">
         <f>G7+G10</f>
         <v>2419989</v>
       </c>
-      <c r="H4" s="58">
+      <c r="H4" s="53">
         <f t="shared" ref="H4:J4" si="2">H7+H10</f>
         <v>2496454</v>
       </c>
-      <c r="I4" s="58">
+      <c r="I4" s="53">
         <f t="shared" si="2"/>
         <v>2575110</v>
       </c>
-      <c r="J4" s="58">
+      <c r="J4" s="53">
         <f t="shared" si="2"/>
         <v>2655942</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A5" s="6" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B5" s="5">
         <f>B8+B11</f>
@@ -1488,26 +1546,26 @@
         <f t="shared" si="3"/>
         <v>2552062</v>
       </c>
-      <c r="G5" s="58">
+      <c r="G5" s="53">
         <f>G8+G11</f>
         <v>2600374</v>
       </c>
-      <c r="H5" s="58">
+      <c r="H5" s="53">
         <f t="shared" ref="H5:J5" si="4">H8+H11</f>
         <v>2683364</v>
       </c>
-      <c r="I5" s="58">
+      <c r="I5" s="53">
         <f t="shared" si="4"/>
         <v>2768781</v>
       </c>
-      <c r="J5" s="58">
+      <c r="J5" s="53">
         <f t="shared" si="4"/>
         <v>2856615</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A6" s="4" t="s">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3">
         <v>303819</v>
@@ -1524,22 +1582,22 @@
       <c r="F6" s="3">
         <v>2641553</v>
       </c>
-      <c r="G6" s="59">
+      <c r="G6" s="54">
         <v>2714419</v>
       </c>
-      <c r="H6" s="59">
+      <c r="H6" s="54">
         <v>2824229</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="54">
         <v>2937788</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="54">
         <v>3055126</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A7" s="6" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="B7" s="5">
         <v>164304</v>
@@ -1556,22 +1614,22 @@
       <c r="F7" s="5">
         <v>1297410</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="53">
         <v>1332828</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="53">
         <v>1386277</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7" s="53">
         <v>1441527</v>
       </c>
-      <c r="J7" s="58">
+      <c r="J7" s="53">
         <v>1498589</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A8" s="6" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="B8" s="5">
         <v>139515</v>
@@ -1588,22 +1646,22 @@
       <c r="F8" s="5">
         <v>1344143</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="53">
         <v>1381591</v>
       </c>
-      <c r="H8" s="58">
+      <c r="H8" s="53">
         <v>1437952</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="53">
         <v>1496261</v>
       </c>
-      <c r="J8" s="58">
+      <c r="J8" s="53">
         <v>1556537</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A9" s="4" t="s">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="B9" s="3">
         <v>1035011</v>
@@ -1622,23 +1680,23 @@
       <c r="F9" s="3">
         <v>2285979</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="54">
         <f>G10+G11</f>
         <v>2305944</v>
       </c>
-      <c r="H9" s="59">
+      <c r="H9" s="54">
         <v>2355589</v>
       </c>
-      <c r="I9" s="59">
+      <c r="I9" s="54">
         <v>2406103</v>
       </c>
-      <c r="J9" s="59">
+      <c r="J9" s="54">
         <v>2457431</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A10" s="6" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="B10" s="5">
         <v>494057</v>
@@ -1655,22 +1713,22 @@
       <c r="F10" s="5">
         <v>1078060</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="53">
         <v>1087161</v>
       </c>
-      <c r="H10" s="58">
+      <c r="H10" s="53">
         <v>1110177</v>
       </c>
-      <c r="I10" s="58">
+      <c r="I10" s="53">
         <v>1133583</v>
       </c>
-      <c r="J10" s="58">
+      <c r="J10" s="53">
         <v>1157353</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A11" s="6" t="s">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="B11" s="5">
         <v>540954</v>
@@ -1687,22 +1745,22 @@
       <c r="F11" s="5">
         <v>1207919</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="53">
         <v>1218783</v>
       </c>
-      <c r="H11" s="58">
+      <c r="H11" s="53">
         <v>1245412</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11" s="53">
         <v>1272520</v>
       </c>
-      <c r="J11" s="58">
+      <c r="J11" s="53">
         <v>1300078</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.85">
-      <c r="A12" s="85" t="s">
-        <v>104</v>
+      <c r="A12" s="80" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1724,24 +1782,22 @@
     <col min="3" max="3" width="13.5546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.109375" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="22.6640625" style="53" customWidth="1"/>
+    <col min="6" max="6" width="22.6640625" style="48" customWidth="1"/>
     <col min="7" max="16384" width="19.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A1" s="63" t="s">
-        <v>72</v>
-      </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="64"/>
+      <c r="A1" s="58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.85">
-      <c r="A2" s="12" t="s">
-        <v>16</v>
-      </c>
+      <c r="A2" s="12"/>
       <c r="B2" s="9">
         <v>1977</v>
       </c>
@@ -1757,16 +1813,16 @@
       <c r="F2" s="9">
         <v>2023</v>
       </c>
-      <c r="G2" s="60">
+      <c r="G2" s="55">
         <v>2024</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="55">
         <v>2025</v>
       </c>
-      <c r="I2" s="60">
+      <c r="I2" s="55">
         <v>2026</v>
       </c>
-      <c r="J2" s="60">
+      <c r="J2" s="55">
         <v>2027</v>
       </c>
     </row>
@@ -1789,22 +1845,22 @@
       <c r="F3" s="11">
         <v>4927532</v>
       </c>
-      <c r="G3" s="62">
+      <c r="G3" s="57">
         <v>5020364</v>
       </c>
-      <c r="H3" s="62">
+      <c r="H3" s="57">
         <v>5179819</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I3" s="57">
         <v>5343892</v>
       </c>
-      <c r="J3" s="62">
+      <c r="J3" s="57">
         <v>5512557</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A4" s="15" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="B4" s="13">
         <v>156721</v>
@@ -1821,22 +1877,22 @@
       <c r="F4" s="13">
         <v>625644</v>
       </c>
-      <c r="G4" s="61">
+      <c r="G4" s="56">
         <v>639601</v>
       </c>
-      <c r="H4" s="61">
+      <c r="H4" s="56">
         <v>661702</v>
       </c>
-      <c r="I4" s="61">
+      <c r="I4" s="56">
         <v>684518</v>
       </c>
-      <c r="J4" s="61">
+      <c r="J4" s="56">
         <v>708056</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A5" s="15" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="B5" s="13">
         <v>124194</v>
@@ -1853,22 +1909,22 @@
       <c r="F5" s="13">
         <v>403091</v>
       </c>
-      <c r="G5" s="61">
+      <c r="G5" s="56">
         <v>410472</v>
       </c>
-      <c r="H5" s="61">
+      <c r="H5" s="56">
         <v>424654</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="56">
         <v>439298</v>
       </c>
-      <c r="J5" s="61">
+      <c r="J5" s="56">
         <v>454404</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A6" s="15" t="s">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B6" s="13">
         <v>129162</v>
@@ -1885,22 +1941,22 @@
       <c r="F6" s="13">
         <v>451804</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="56">
         <v>460005</v>
       </c>
-      <c r="H6" s="61">
+      <c r="H6" s="56">
         <v>474432</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="56">
         <v>489331</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="56">
         <v>504702</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A7" s="15" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="B7" s="13">
         <v>149432</v>
@@ -1917,22 +1973,22 @@
       <c r="F7" s="13">
         <v>442490</v>
       </c>
-      <c r="G7" s="61">
+      <c r="G7" s="56">
         <v>452087</v>
       </c>
-      <c r="H7" s="61">
+      <c r="H7" s="56">
         <v>468996</v>
       </c>
-      <c r="I7" s="61">
+      <c r="I7" s="56">
         <v>486615</v>
       </c>
-      <c r="J7" s="61">
+      <c r="J7" s="56">
         <v>504955</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A8" s="15" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="B8" s="13">
         <v>151353</v>
@@ -1949,22 +2005,22 @@
       <c r="F8" s="13">
         <v>391310</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="56">
         <v>399199</v>
       </c>
-      <c r="H8" s="61">
+      <c r="H8" s="56">
         <v>411783</v>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="56">
         <v>424743</v>
       </c>
-      <c r="J8" s="61">
+      <c r="J8" s="56">
         <v>438075</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A9" s="15" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="B9" s="13">
         <v>216008</v>
@@ -1981,22 +2037,22 @@
       <c r="F9" s="13">
         <v>323903</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="56">
         <v>329238</v>
       </c>
-      <c r="H9" s="61">
+      <c r="H9" s="56">
         <v>339617</v>
       </c>
-      <c r="I9" s="61">
+      <c r="I9" s="56">
         <v>350306</v>
       </c>
-      <c r="J9" s="61">
+      <c r="J9" s="56">
         <v>361303</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A10" s="15" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="B10" s="13">
         <v>55354</v>
@@ -2013,22 +2069,22 @@
       <c r="F10" s="13">
         <v>71623</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="56">
         <v>71730</v>
       </c>
-      <c r="H10" s="61">
+      <c r="H10" s="56">
         <v>73291</v>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="56">
         <v>74882</v>
       </c>
-      <c r="J10" s="61">
+      <c r="J10" s="56">
         <v>76502</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A11" s="15" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="B11" s="13">
         <v>53526</v>
@@ -2045,22 +2101,22 @@
       <c r="F11" s="13">
         <v>184459</v>
       </c>
-      <c r="G11" s="61">
+      <c r="G11" s="56">
         <v>186954</v>
       </c>
-      <c r="H11" s="61">
+      <c r="H11" s="56">
         <v>191413</v>
       </c>
-      <c r="I11" s="61">
+      <c r="I11" s="56">
         <v>195933</v>
       </c>
-      <c r="J11" s="61">
+      <c r="J11" s="56">
         <v>200513</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A12" s="15" t="s">
-        <v>8</v>
+        <v>101</v>
       </c>
       <c r="B12" s="13">
         <v>74980</v>
@@ -2077,22 +2133,22 @@
       <c r="F12" s="13">
         <v>114759</v>
       </c>
-      <c r="G12" s="61">
+      <c r="G12" s="56">
         <v>117017</v>
       </c>
-      <c r="H12" s="61">
+      <c r="H12" s="56">
         <v>120687</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="56">
         <v>124477</v>
       </c>
-      <c r="J12" s="61">
+      <c r="J12" s="56">
         <v>128388</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A13" s="15" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="B13" s="13">
         <v>83231</v>
@@ -2109,22 +2165,22 @@
       <c r="F13" s="13">
         <v>363075</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G13" s="56">
         <v>371741</v>
       </c>
-      <c r="H13" s="61">
+      <c r="H13" s="56">
         <v>385646</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="56">
         <v>400133</v>
       </c>
-      <c r="J13" s="61">
+      <c r="J13" s="56">
         <v>415213</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A14" s="15" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="B14" s="13">
         <v>22554</v>
@@ -2141,22 +2197,22 @@
       <c r="F14" s="13">
         <v>79129</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="56">
         <v>80657</v>
       </c>
-      <c r="H14" s="61">
+      <c r="H14" s="56">
         <v>82414</v>
       </c>
-      <c r="I14" s="61">
+      <c r="I14" s="56">
         <v>84202</v>
       </c>
-      <c r="J14" s="61">
+      <c r="J14" s="56">
         <v>86023</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A15" s="15" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="B15" s="13">
         <v>17611</v>
@@ -2173,22 +2229,22 @@
       <c r="F15" s="13">
         <v>29483</v>
       </c>
-      <c r="G15" s="61">
+      <c r="G15" s="56">
         <v>30074</v>
       </c>
-      <c r="H15" s="61">
+      <c r="H15" s="56">
         <v>30729</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="56">
         <v>31396</v>
       </c>
-      <c r="J15" s="61">
+      <c r="J15" s="56">
         <v>32075</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A16" s="15" t="s">
-        <v>3</v>
+        <v>105</v>
       </c>
       <c r="B16" s="13">
         <v>134704</v>
@@ -2206,26 +2262,26 @@
         <f>SUM(F17:F19)</f>
         <v>1446761</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="56">
         <f>SUM(G17:G19)</f>
         <v>1471589</v>
       </c>
-      <c r="H16" s="61">
+      <c r="H16" s="56">
         <f>SUM(H17:H19)</f>
         <v>1514455</v>
       </c>
-      <c r="I16" s="61">
+      <c r="I16" s="56">
         <f>SUM(I17:I19)</f>
         <v>1558058</v>
       </c>
-      <c r="J16" s="61">
+      <c r="J16" s="56">
         <f>SUM(J17:J19)</f>
         <v>1602348</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A17" s="14" t="s">
-        <v>71</v>
+        <v>106</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2234,22 +2290,22 @@
       <c r="F17" s="13">
         <v>204881</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="56">
         <v>205528</v>
       </c>
-      <c r="H17" s="61">
+      <c r="H17" s="56">
         <v>211515</v>
       </c>
-      <c r="I17" s="61">
+      <c r="I17" s="56">
         <v>217605</v>
       </c>
-      <c r="J17" s="61">
+      <c r="J17" s="56">
         <v>223791</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A18" s="14" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2258,22 +2314,22 @@
       <c r="F18" s="13">
         <v>614465</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="56">
         <v>629149</v>
       </c>
-      <c r="H18" s="61">
+      <c r="H18" s="56">
         <v>647476</v>
       </c>
-      <c r="I18" s="61">
+      <c r="I18" s="56">
         <v>666117</v>
       </c>
-      <c r="J18" s="61">
+      <c r="J18" s="56">
         <v>685052</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A19" s="14" t="s">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2282,24 +2338,24 @@
       <c r="F19" s="13">
         <v>627415</v>
       </c>
-      <c r="G19" s="61">
+      <c r="G19" s="56">
         <v>636912</v>
       </c>
-      <c r="H19" s="61">
+      <c r="H19" s="56">
         <v>655464</v>
       </c>
-      <c r="I19" s="61">
+      <c r="I19" s="56">
         <v>674336</v>
       </c>
-      <c r="J19" s="61">
+      <c r="J19" s="56">
         <v>693505</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.85">
-      <c r="A20" s="85" t="s">
-        <v>104</v>
-      </c>
-      <c r="F20" s="52"/>
+      <c r="A20" s="80" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2322,7 +2378,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="25" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -2336,7 +2392,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A2" s="24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="23">
         <v>1977</v>
@@ -2353,16 +2409,16 @@
       <c r="F2" s="22">
         <v>2023</v>
       </c>
-      <c r="G2" s="67">
+      <c r="G2" s="62">
         <v>2024</v>
       </c>
-      <c r="H2" s="67">
+      <c r="H2" s="62">
         <v>2025</v>
       </c>
-      <c r="I2" s="67">
+      <c r="I2" s="62">
         <v>2026</v>
       </c>
-      <c r="J2" s="67">
+      <c r="J2" s="62">
         <v>2027</v>
       </c>
     </row>
@@ -2388,22 +2444,22 @@
       <c r="F3" s="18">
         <v>4927532</v>
       </c>
-      <c r="G3" s="68">
+      <c r="G3" s="63">
         <v>5020364</v>
       </c>
-      <c r="H3" s="68">
+      <c r="H3" s="63">
         <v>5179819</v>
       </c>
-      <c r="I3" s="68">
+      <c r="I3" s="63">
         <v>5343892</v>
       </c>
-      <c r="J3" s="68">
+      <c r="J3" s="63">
         <v>5512557</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A4" s="20" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B4" s="21">
         <v>216787</v>
@@ -2420,22 +2476,22 @@
       <c r="F4" s="19">
         <v>701956</v>
       </c>
-      <c r="G4" s="69">
+      <c r="G4" s="64">
         <v>715433</v>
       </c>
-      <c r="H4" s="69">
+      <c r="H4" s="64">
         <v>738477</v>
       </c>
-      <c r="I4" s="69">
+      <c r="I4" s="64">
         <v>762215</v>
       </c>
-      <c r="J4" s="69">
+      <c r="J4" s="64">
         <v>786643</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A5" s="20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="7">
         <v>219206</v>
@@ -2452,22 +2508,22 @@
       <c r="F5" s="19">
         <v>689924</v>
       </c>
-      <c r="G5" s="69">
+      <c r="G5" s="64">
         <v>703184</v>
       </c>
-      <c r="H5" s="69">
+      <c r="H5" s="64">
         <v>725843</v>
       </c>
-      <c r="I5" s="69">
+      <c r="I5" s="64">
         <v>749184</v>
       </c>
-      <c r="J5" s="69">
+      <c r="J5" s="64">
         <v>773205</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B6" s="7">
         <v>152665</v>
@@ -2484,22 +2540,22 @@
       <c r="F6" s="19">
         <v>654585</v>
       </c>
-      <c r="G6" s="69">
+      <c r="G6" s="64">
         <v>667092</v>
       </c>
-      <c r="H6" s="69">
+      <c r="H6" s="64">
         <v>688503</v>
       </c>
-      <c r="I6" s="69">
+      <c r="I6" s="64">
         <v>710553</v>
       </c>
-      <c r="J6" s="69">
+      <c r="J6" s="64">
         <v>733240</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A7" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B7" s="7">
         <v>138274</v>
@@ -2516,22 +2572,22 @@
       <c r="F7" s="19">
         <v>563050</v>
       </c>
-      <c r="G7" s="69">
+      <c r="G7" s="64">
         <v>573700</v>
       </c>
-      <c r="H7" s="69">
+      <c r="H7" s="64">
         <v>591983</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="64">
         <v>610799</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="64">
         <v>630146</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A8" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="7">
         <v>111318</v>
@@ -2548,22 +2604,22 @@
       <c r="F8" s="19">
         <v>420572</v>
       </c>
-      <c r="G8" s="69">
+      <c r="G8" s="64">
         <v>428410</v>
       </c>
-      <c r="H8" s="69">
+      <c r="H8" s="64">
         <v>441891</v>
       </c>
-      <c r="I8" s="69">
+      <c r="I8" s="64">
         <v>455751</v>
       </c>
-      <c r="J8" s="69">
+      <c r="J8" s="64">
         <v>469986</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A9" s="7" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B9" s="7">
         <v>89029</v>
@@ -2580,22 +2636,22 @@
       <c r="F9" s="19">
         <v>348210</v>
       </c>
-      <c r="G9" s="69">
+      <c r="G9" s="64">
         <v>354640</v>
       </c>
-      <c r="H9" s="69">
+      <c r="H9" s="64">
         <v>365720</v>
       </c>
-      <c r="I9" s="69">
+      <c r="I9" s="64">
         <v>377106</v>
       </c>
-      <c r="J9" s="69">
+      <c r="J9" s="64">
         <v>388796</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A10" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" s="7">
         <v>73724</v>
@@ -2612,22 +2668,22 @@
       <c r="F10" s="19">
         <v>300641</v>
       </c>
-      <c r="G10" s="69">
+      <c r="G10" s="64">
         <v>306200</v>
       </c>
-      <c r="H10" s="69">
+      <c r="H10" s="64">
         <v>315776</v>
       </c>
-      <c r="I10" s="69">
+      <c r="I10" s="64">
         <v>325618</v>
       </c>
-      <c r="J10" s="69">
+      <c r="J10" s="64">
         <v>335722</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A11" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" s="7">
         <v>61709</v>
@@ -2644,22 +2700,22 @@
       <c r="F11" s="19">
         <v>255667</v>
       </c>
-      <c r="G11" s="69">
+      <c r="G11" s="64">
         <v>260378</v>
       </c>
-      <c r="H11" s="69">
+      <c r="H11" s="64">
         <v>268483</v>
       </c>
-      <c r="I11" s="69">
+      <c r="I11" s="64">
         <v>276809</v>
       </c>
-      <c r="J11" s="69">
+      <c r="J11" s="64">
         <v>285355</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A12" s="7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B12" s="7">
         <v>68686</v>
@@ -2676,22 +2732,22 @@
       <c r="F12" s="19">
         <v>209012</v>
       </c>
-      <c r="G12" s="69">
+      <c r="G12" s="64">
         <v>212865</v>
       </c>
-      <c r="H12" s="69">
+      <c r="H12" s="64">
         <v>219508</v>
       </c>
-      <c r="I12" s="69">
+      <c r="I12" s="64">
         <v>226333</v>
       </c>
-      <c r="J12" s="69">
+      <c r="J12" s="64">
         <v>233339</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A13" s="7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13" s="7">
         <v>47843</v>
@@ -2708,22 +2764,22 @@
       <c r="F13" s="19">
         <v>178985</v>
       </c>
-      <c r="G13" s="69">
+      <c r="G13" s="64">
         <v>182286</v>
       </c>
-      <c r="H13" s="69">
+      <c r="H13" s="64">
         <v>187978</v>
       </c>
-      <c r="I13" s="69">
+      <c r="I13" s="64">
         <v>193827</v>
       </c>
-      <c r="J13" s="69">
+      <c r="J13" s="64">
         <v>199832</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A14" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14" s="7">
         <v>47120</v>
@@ -2740,22 +2796,22 @@
       <c r="F14" s="19">
         <v>158330</v>
       </c>
-      <c r="G14" s="69">
+      <c r="G14" s="64">
         <v>161269</v>
       </c>
-      <c r="H14" s="69">
+      <c r="H14" s="64">
         <v>166338</v>
       </c>
-      <c r="I14" s="69">
+      <c r="I14" s="64">
         <v>171550</v>
       </c>
-      <c r="J14" s="69">
+      <c r="J14" s="64">
         <v>176904</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A15" s="7" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="7">
         <v>34398</v>
@@ -2772,22 +2828,22 @@
       <c r="F15" s="19">
         <v>133645</v>
       </c>
-      <c r="G15" s="69">
+      <c r="G15" s="64">
         <v>136104</v>
       </c>
-      <c r="H15" s="69">
+      <c r="H15" s="64">
         <v>140373</v>
       </c>
-      <c r="I15" s="69">
+      <c r="I15" s="64">
         <v>144762</v>
       </c>
-      <c r="J15" s="69">
+      <c r="J15" s="64">
         <v>149269</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A16" s="7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="7">
         <v>27262</v>
@@ -2804,22 +2860,22 @@
       <c r="F16" s="19">
         <v>108127</v>
       </c>
-      <c r="G16" s="69">
+      <c r="G16" s="64">
         <v>110144</v>
       </c>
-      <c r="H16" s="69">
+      <c r="H16" s="64">
         <v>113632</v>
       </c>
-      <c r="I16" s="69">
+      <c r="I16" s="64">
         <v>117221</v>
       </c>
-      <c r="J16" s="69">
+      <c r="J16" s="64">
         <v>120910</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A17" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B17" s="7">
         <v>14572</v>
@@ -2836,22 +2892,22 @@
       <c r="F17" s="19">
         <v>81901</v>
       </c>
-      <c r="G17" s="69">
+      <c r="G17" s="64">
         <v>83411</v>
       </c>
-      <c r="H17" s="69">
+      <c r="H17" s="64">
         <v>86042</v>
       </c>
-      <c r="I17" s="69">
+      <c r="I17" s="64">
         <v>88748</v>
       </c>
-      <c r="J17" s="69">
+      <c r="J17" s="64">
         <v>91529</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A18" s="7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B18" s="7">
         <v>18414</v>
@@ -2868,22 +2924,22 @@
       <c r="F18" s="19">
         <v>55037</v>
       </c>
-      <c r="G18" s="69">
+      <c r="G18" s="64">
         <v>56068</v>
       </c>
-      <c r="H18" s="69">
+      <c r="H18" s="64">
         <v>57858</v>
       </c>
-      <c r="I18" s="69">
+      <c r="I18" s="64">
         <v>59700</v>
       </c>
-      <c r="J18" s="69">
+      <c r="J18" s="64">
         <v>61595</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A19" s="7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B19" s="7">
         <v>17823</v>
@@ -2900,22 +2956,22 @@
       <c r="F19" s="19">
         <v>67891</v>
       </c>
-      <c r="G19" s="69">
+      <c r="G19" s="64">
         <v>69179</v>
       </c>
-      <c r="H19" s="69">
+      <c r="H19" s="64">
         <v>71413</v>
       </c>
-      <c r="I19" s="69">
+      <c r="I19" s="64">
         <v>73716</v>
       </c>
-      <c r="J19" s="69">
+      <c r="J19" s="64">
         <v>76086</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.85">
-      <c r="A20" s="85" t="s">
-        <v>104</v>
+      <c r="A20" s="80" t="s">
+        <v>81</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
@@ -2954,7 +3010,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="25" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -2963,174 +3019,174 @@
       <c r="F1" s="25"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.85">
-      <c r="A2" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="49" t="s">
-        <v>58</v>
+      <c r="A2" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>50</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D2" s="49" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="49" t="s">
-        <v>60</v>
+        <v>76</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>61</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>62</v>
+        <v>75</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>53</v>
+      </c>
+      <c r="H2" s="44" t="s">
+        <v>54</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="J2" s="49" t="s">
-        <v>63</v>
+        <v>74</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>55</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.85">
       <c r="A3" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="61">
+        <v>66</v>
+      </c>
+      <c r="C3" s="61">
+        <v>82</v>
+      </c>
+      <c r="D3" s="61">
+        <v>74</v>
+      </c>
+      <c r="E3" s="61">
+        <v>66</v>
+      </c>
+      <c r="F3" s="61">
+        <v>78</v>
+      </c>
+      <c r="G3" s="61">
+        <v>72</v>
+      </c>
+      <c r="H3" s="61">
+        <v>29</v>
+      </c>
+      <c r="I3" s="61">
         <v>36</v>
       </c>
-      <c r="B3" s="66">
-        <v>66</v>
-      </c>
-      <c r="C3" s="66">
-        <v>82</v>
-      </c>
-      <c r="D3" s="66">
-        <v>74</v>
-      </c>
-      <c r="E3" s="66">
-        <v>66</v>
-      </c>
-      <c r="F3" s="66">
-        <v>78</v>
-      </c>
-      <c r="G3" s="66">
-        <v>72</v>
-      </c>
-      <c r="H3" s="66">
-        <v>29</v>
-      </c>
-      <c r="I3" s="66">
-        <v>36</v>
-      </c>
-      <c r="J3" s="66">
+      <c r="J3" s="61">
         <v>33</v>
       </c>
-      <c r="K3" s="66">
+      <c r="K3" s="61">
         <v>32.1</v>
       </c>
-      <c r="L3" s="66">
+      <c r="L3" s="61">
         <v>34.4</v>
       </c>
-      <c r="M3" s="66">
+      <c r="M3" s="61">
         <v>33.299999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.85">
       <c r="A4" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="66">
+        <v>33</v>
+      </c>
+      <c r="B4" s="61">
         <v>43</v>
       </c>
-      <c r="C4" s="66">
+      <c r="C4" s="61">
         <v>49</v>
       </c>
-      <c r="D4" s="66">
+      <c r="D4" s="61">
         <v>46</v>
       </c>
-      <c r="E4" s="66">
+      <c r="E4" s="61">
         <v>40</v>
       </c>
-      <c r="F4" s="66">
+      <c r="F4" s="61">
         <v>51</v>
       </c>
-      <c r="G4" s="66">
+      <c r="G4" s="61">
         <v>46</v>
       </c>
-      <c r="H4" s="66">
+      <c r="H4" s="61">
         <v>8</v>
       </c>
-      <c r="I4" s="66">
+      <c r="I4" s="61">
         <v>9</v>
       </c>
-      <c r="J4" s="66">
+      <c r="J4" s="61">
         <v>8</v>
       </c>
-      <c r="K4" s="66">
+      <c r="K4" s="61">
         <v>13.3</v>
       </c>
-      <c r="L4" s="66">
+      <c r="L4" s="61">
         <v>12.1</v>
       </c>
-      <c r="M4" s="66">
+      <c r="M4" s="61">
         <v>12.7</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.85">
       <c r="A5" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="66">
+        <v>32</v>
+      </c>
+      <c r="B5" s="61">
         <v>106</v>
       </c>
-      <c r="C5" s="66">
+      <c r="C5" s="61">
         <v>127</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="61">
         <v>116</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="61">
         <v>103</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="61">
         <v>125</v>
       </c>
-      <c r="G5" s="66">
+      <c r="G5" s="61">
         <v>115</v>
       </c>
-      <c r="H5" s="66">
+      <c r="H5" s="61">
         <v>37</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="61">
         <v>45</v>
       </c>
-      <c r="J5" s="66">
+      <c r="J5" s="61">
         <v>41</v>
       </c>
-      <c r="K5" s="66">
+      <c r="K5" s="61">
         <f>([1]National!$E$97+[1]National!$E$98)*1000</f>
         <v>45.657286310875925</v>
       </c>
-      <c r="L5" s="66">
+      <c r="L5" s="61">
         <f>([1]National!$E$60+[1]National!$E$61)*1000</f>
         <v>46.647236360742802</v>
       </c>
-      <c r="M5" s="66">
+      <c r="M5" s="61">
         <v>46.152261335809364</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.85">
-      <c r="A6" s="51" t="s">
-        <v>105</v>
+      <c r="A6" s="46" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.85">
@@ -3166,18 +3222,18 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="30.88671875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="74" customWidth="1"/>
-    <col min="3" max="4" width="31.6640625" style="74" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
     <col min="5" max="16384" width="11.5546875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+        <v>84</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3191,278 +3247,278 @@
       <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A2" s="50" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>66</v>
+      <c r="A2" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="72">
+      <c r="B3" s="67">
         <v>1</v>
       </c>
-      <c r="C3" s="72">
+      <c r="C3" s="67">
         <v>1</v>
       </c>
-      <c r="D3" s="72">
+      <c r="D3" s="67">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="73">
+        <v>30</v>
+      </c>
+      <c r="B4" s="68">
         <v>0.15019773378675499</v>
       </c>
-      <c r="C4" s="73">
+      <c r="C4" s="68">
         <v>0.1352497941416286</v>
       </c>
-      <c r="D4" s="73">
+      <c r="D4" s="68">
         <v>0.14245591469258082</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="73">
+        <v>40</v>
+      </c>
+      <c r="B5" s="68">
         <v>0.14653420973582504</v>
       </c>
-      <c r="C5" s="73">
+      <c r="C5" s="68">
         <v>0.13394503770824412</v>
       </c>
-      <c r="D5" s="73">
+      <c r="D5" s="68">
         <v>0.14001404075614515</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="73">
+        <v>39</v>
+      </c>
+      <c r="B6" s="68">
         <v>0.13739234976245948</v>
       </c>
-      <c r="C6" s="73">
+      <c r="C6" s="68">
         <v>0.12860712771846924</v>
       </c>
-      <c r="D6" s="73">
+      <c r="D6" s="68">
         <v>0.13284231802581759</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="73">
+        <v>38</v>
+      </c>
+      <c r="B7" s="68">
         <v>0.11496828521397703</v>
       </c>
-      <c r="C7" s="73">
+      <c r="C7" s="68">
         <v>0.11361249162304529</v>
       </c>
-      <c r="D7" s="73">
+      <c r="D7" s="68">
         <v>0.11426609421129681</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="73">
+        <v>26</v>
+      </c>
+      <c r="B8" s="68">
         <v>7.9665661184978614E-2</v>
       </c>
-      <c r="C8" s="73">
+      <c r="C8" s="68">
         <v>9.0643644153031014E-2</v>
       </c>
-      <c r="D8" s="73">
+      <c r="D8" s="68">
         <v>8.5351365044156691E-2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="73">
+        <v>25</v>
+      </c>
+      <c r="B9" s="68">
         <v>6.4186013214147894E-2</v>
       </c>
-      <c r="C9" s="73">
+      <c r="C9" s="68">
         <v>7.6698085181093917E-2</v>
       </c>
-      <c r="D9" s="73">
+      <c r="D9" s="68">
         <v>7.0666250620934734E-2</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="73">
+        <v>24</v>
+      </c>
+      <c r="B10" s="68">
         <v>5.591810465081945E-2</v>
       </c>
-      <c r="C10" s="73">
+      <c r="C10" s="68">
         <v>6.5754475814841201E-2</v>
       </c>
-      <c r="D10" s="73">
+      <c r="D10" s="68">
         <v>6.1012546285096246E-2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="73">
+        <v>23</v>
+      </c>
+      <c r="B11" s="68">
         <v>4.8336952175404693E-2</v>
       </c>
-      <c r="C11" s="73">
+      <c r="C11" s="68">
         <v>5.5188342892053432E-2</v>
       </c>
-      <c r="D11" s="73">
+      <c r="D11" s="68">
         <v>5.1885416292610474E-2</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="73">
+        <v>22</v>
+      </c>
+      <c r="B12" s="68">
         <v>4.1175387640228434E-2</v>
       </c>
-      <c r="C12" s="73">
+      <c r="C12" s="68">
         <v>4.3573113700768253E-2</v>
       </c>
-      <c r="D12" s="73">
+      <c r="D12" s="68">
         <v>4.2417215064534643E-2</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="73">
+        <v>21</v>
+      </c>
+      <c r="B13" s="68">
         <v>3.59976668738025E-2</v>
       </c>
-      <c r="C13" s="73">
+      <c r="C13" s="68">
         <v>3.66268739322008E-2</v>
       </c>
-      <c r="D13" s="73">
+      <c r="D13" s="68">
         <v>3.6323545043498134E-2</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="73">
+        <v>20</v>
+      </c>
+      <c r="B14" s="68">
         <v>3.1990881120045618E-2</v>
       </c>
-      <c r="C14" s="73">
+      <c r="C14" s="68">
         <v>3.2262922638433389E-2</v>
       </c>
-      <c r="D14" s="73">
+      <c r="D14" s="68">
         <v>3.2131776538772014E-2</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="73">
+        <v>19</v>
+      </c>
+      <c r="B15" s="68">
         <v>2.744503612546377E-2</v>
       </c>
-      <c r="C15" s="73">
+      <c r="C15" s="68">
         <v>2.6821305902556256E-2</v>
       </c>
-      <c r="D15" s="73">
+      <c r="D15" s="68">
         <v>2.7121994511212125E-2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="73">
+        <v>18</v>
+      </c>
+      <c r="B16" s="68">
         <v>2.2813682775715161E-2</v>
       </c>
-      <c r="C16" s="73">
+      <c r="C16" s="68">
         <v>2.1133319518059718E-2</v>
       </c>
-      <c r="D16" s="73">
+      <c r="D16" s="68">
         <v>2.1943391038872315E-2</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="73">
+        <v>17</v>
+      </c>
+      <c r="B17" s="68">
         <v>1.7500329239129826E-2</v>
       </c>
-      <c r="C17" s="73">
+      <c r="C17" s="68">
         <v>1.5802583138069613E-2</v>
       </c>
-      <c r="D17" s="73">
+      <c r="D17" s="68">
         <v>1.6621034600840572E-2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="73">
+        <v>16</v>
+      </c>
+      <c r="B18" s="68">
         <v>1.1843244518614555E-2</v>
       </c>
-      <c r="C18" s="73">
+      <c r="C18" s="68">
         <v>1.0541807658724582E-2</v>
       </c>
-      <c r="D18" s="73">
+      <c r="D18" s="68">
         <v>1.1169205890429929E-2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="73">
+        <v>37</v>
+      </c>
+      <c r="B19" s="68">
         <v>5.943293015444771E-3</v>
       </c>
-      <c r="C19" s="73">
+      <c r="C19" s="68">
         <v>5.4016342906763716E-3</v>
       </c>
-      <c r="D19" s="73">
+      <c r="D19" s="68">
         <v>5.662757773934708E-3</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="73">
+        <v>36</v>
+      </c>
+      <c r="B20" s="68">
         <v>8.0911689664886523E-3</v>
       </c>
-      <c r="C20" s="73">
+      <c r="C20" s="68">
         <v>8.1374399890821528E-3</v>
       </c>
-      <c r="D20" s="73">
+      <c r="D20" s="68">
         <v>8.1151335992914707E-3</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A21" s="16" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="B24" s="75"/>
+      <c r="B24" s="70"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3476,18 +3532,18 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="30.88671875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="74" customWidth="1"/>
-    <col min="3" max="4" width="31.6640625" style="74" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
     <col min="5" max="16384" width="11.5546875" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A1" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+        <v>78</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3501,278 +3557,278 @@
       <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.85">
-      <c r="A2" s="76" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>66</v>
+      <c r="A2" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A3" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="74">
         <v>2375470</v>
       </c>
-      <c r="C3" s="79">
+      <c r="C3" s="74">
         <v>2552062</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="74">
         <v>4927532</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="77">
+        <v>30</v>
+      </c>
+      <c r="B4" s="72">
         <v>356790</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="72">
         <v>345166</v>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="72">
         <v>701956</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="77">
+        <v>40</v>
+      </c>
+      <c r="B5" s="72">
         <v>348088</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="72">
         <v>341836</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="72">
         <v>689924</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A6" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="77">
+        <v>39</v>
+      </c>
+      <c r="B6" s="72">
         <v>326371</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="72">
         <v>328214</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="72">
         <v>654585</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B7" s="77">
+        <v>38</v>
+      </c>
+      <c r="B7" s="72">
         <v>273104</v>
       </c>
-      <c r="C7" s="77">
+      <c r="C7" s="72">
         <v>289946</v>
       </c>
-      <c r="D7" s="77">
+      <c r="D7" s="72">
         <v>563050</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="77">
+        <v>26</v>
+      </c>
+      <c r="B8" s="72">
         <v>189243</v>
       </c>
-      <c r="C8" s="77">
+      <c r="C8" s="72">
         <v>231328</v>
       </c>
-      <c r="D8" s="77">
+      <c r="D8" s="72">
         <v>420572</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A9" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="77">
+        <v>25</v>
+      </c>
+      <c r="B9" s="72">
         <v>152472</v>
       </c>
-      <c r="C9" s="77">
+      <c r="C9" s="72">
         <v>195738</v>
       </c>
-      <c r="D9" s="77">
+      <c r="D9" s="72">
         <v>348210</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="77">
+        <v>24</v>
+      </c>
+      <c r="B10" s="72">
         <v>132832</v>
       </c>
-      <c r="C10" s="77">
+      <c r="C10" s="72">
         <v>167809</v>
       </c>
-      <c r="D10" s="77">
+      <c r="D10" s="72">
         <v>300641</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="77">
+        <v>23</v>
+      </c>
+      <c r="B11" s="72">
         <v>114823</v>
       </c>
-      <c r="C11" s="77">
+      <c r="C11" s="72">
         <v>140844</v>
       </c>
-      <c r="D11" s="77">
+      <c r="D11" s="72">
         <v>255667</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="77">
+        <v>22</v>
+      </c>
+      <c r="B12" s="72">
         <v>97811</v>
       </c>
-      <c r="C12" s="77">
+      <c r="C12" s="72">
         <v>111201</v>
       </c>
-      <c r="D12" s="77">
+      <c r="D12" s="72">
         <v>209012</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A13" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="77">
+        <v>21</v>
+      </c>
+      <c r="B13" s="72">
         <v>85511</v>
       </c>
-      <c r="C13" s="77">
+      <c r="C13" s="72">
         <v>93474</v>
       </c>
-      <c r="D13" s="77">
+      <c r="D13" s="72">
         <v>178985</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A14" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="77">
+        <v>20</v>
+      </c>
+      <c r="B14" s="72">
         <v>75993</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="72">
         <v>82337</v>
       </c>
-      <c r="D14" s="77">
+      <c r="D14" s="72">
         <v>158330</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="77">
+        <v>19</v>
+      </c>
+      <c r="B15" s="72">
         <v>65195</v>
       </c>
-      <c r="C15" s="77">
+      <c r="C15" s="72">
         <v>68450</v>
       </c>
-      <c r="D15" s="77">
+      <c r="D15" s="72">
         <v>133645</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="77">
+        <v>18</v>
+      </c>
+      <c r="B16" s="72">
         <v>54193</v>
       </c>
-      <c r="C16" s="77">
+      <c r="C16" s="72">
         <v>53934</v>
       </c>
-      <c r="D16" s="77">
+      <c r="D16" s="72">
         <v>108127</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A17" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="77">
+        <v>17</v>
+      </c>
+      <c r="B17" s="72">
         <v>41572</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="72">
         <v>40329</v>
       </c>
-      <c r="D17" s="77">
+      <c r="D17" s="72">
         <v>81901</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A18" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="77">
+        <v>16</v>
+      </c>
+      <c r="B18" s="72">
         <v>28133</v>
       </c>
-      <c r="C18" s="77">
+      <c r="C18" s="72">
         <v>26903</v>
       </c>
-      <c r="D18" s="77">
+      <c r="D18" s="72">
         <v>55037</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A19" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="77">
+        <v>37</v>
+      </c>
+      <c r="B19" s="72">
         <v>14118</v>
       </c>
-      <c r="C19" s="77">
+      <c r="C19" s="72">
         <v>13785</v>
       </c>
-      <c r="D19" s="77">
+      <c r="D19" s="72">
         <v>27903</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A20" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="77">
+        <v>36</v>
+      </c>
+      <c r="B20" s="72">
         <v>19220</v>
       </c>
-      <c r="C20" s="77">
+      <c r="C20" s="72">
         <v>20767</v>
       </c>
-      <c r="D20" s="77">
+      <c r="D20" s="72">
         <v>39988</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.85">
       <c r="A21" s="16" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="B24" s="75"/>
+      <c r="B24" s="70"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3786,8 +3842,8 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
   <cols>
     <col min="1" max="1" width="24" style="29" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="74" customWidth="1"/>
-    <col min="3" max="4" width="31.6640625" style="74" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" style="29"/>
     <col min="6" max="8" width="15.6640625" style="29" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="11.5546875" style="29"/>
@@ -3795,11 +3851,11 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A1" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="70"/>
-      <c r="C1" s="70"/>
-      <c r="D1" s="70"/>
+        <v>79</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
       <c r="G1" s="31"/>
@@ -3813,91 +3869,91 @@
       <c r="O1" s="31"/>
     </row>
     <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.85">
-      <c r="A2" s="76" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="81" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="80" t="s">
+      <c r="A2" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="76" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="79">
+      <c r="B3" s="74">
         <v>2375470</v>
       </c>
-      <c r="C3" s="79">
+      <c r="C3" s="74">
         <v>2552062</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="74">
         <v>4927532</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A4" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B4" s="77">
+        <v>72</v>
+      </c>
+      <c r="B4" s="72">
         <v>1031249</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="72">
         <v>1015215</v>
       </c>
-      <c r="D4" s="77">
+      <c r="D4" s="72">
         <v>2046465</v>
       </c>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A5" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B5" s="77">
+        <v>73</v>
+      </c>
+      <c r="B5" s="72">
         <v>1241178</v>
       </c>
-      <c r="C5" s="77">
+      <c r="C5" s="72">
         <v>1435061</v>
       </c>
-      <c r="D5" s="77">
+      <c r="D5" s="72">
         <v>2676239</v>
       </c>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A6" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="77">
+        <v>71</v>
+      </c>
+      <c r="B6" s="72">
         <v>103043</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="72">
         <v>101785</v>
       </c>
-      <c r="D6" s="77">
+      <c r="D6" s="72">
         <v>204828</v>
       </c>
-      <c r="F6" s="82"/>
-      <c r="G6" s="78"/>
-      <c r="H6" s="78"/>
+      <c r="F6" s="77"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.85">
       <c r="A7" s="16" t="s">
-        <v>106</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="B10" s="75"/>
+      <c r="B10" s="70"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3907,10 +3963,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12B744F-6F17-4891-BC34-B3B89A801878}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="1" max="1" width="61.33203125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="97.88671875" style="32" bestFit="1" customWidth="1"/>
     <col min="2" max="8" width="16.44140625" style="32" customWidth="1"/>
     <col min="9" max="9" width="18.6640625" style="32" customWidth="1"/>
     <col min="10" max="10" width="21.5546875" style="32" customWidth="1"/>
@@ -3918,436 +3974,386 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="44" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="42"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A2" s="38"/>
-      <c r="B2" s="37">
+      <c r="A1" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="39"/>
+    </row>
+    <row r="2" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="84"/>
+      <c r="B2" s="83">
         <v>1977</v>
       </c>
-      <c r="C2" s="37">
+      <c r="C2" s="83">
         <v>1988</v>
       </c>
-      <c r="D2" s="37">
+      <c r="D2" s="83">
         <v>2000</v>
       </c>
-      <c r="E2" s="37">
+      <c r="E2" s="83">
         <v>2013</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="83">
         <v>2015</v>
       </c>
-      <c r="G2" s="37">
+      <c r="G2" s="83">
         <v>2019</v>
       </c>
-      <c r="H2" s="37">
+      <c r="H2" s="83">
         <v>2023</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A3" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39" t="s">
+    <row r="3" spans="1:8" ht="27" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35">
+        <v>6.3</v>
+      </c>
+      <c r="D3" s="35">
+        <v>5</v>
+      </c>
+      <c r="E3" s="35">
+        <v>4.3</v>
+      </c>
+      <c r="F3" s="35">
+        <v>3.84</v>
+      </c>
+      <c r="G3" s="35">
+        <v>5.2</v>
+      </c>
+      <c r="H3" s="60">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29.4" x14ac:dyDescent="0.7">
+      <c r="A4" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="35">
+        <v>49</v>
+      </c>
+      <c r="C4" s="35">
+        <v>45.2</v>
+      </c>
+      <c r="D4" s="35">
+        <v>36</v>
+      </c>
+      <c r="E4" s="35">
+        <v>32</v>
+      </c>
+      <c r="F4" s="35">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="G4" s="35">
+        <v>35.5</v>
+      </c>
+      <c r="H4" s="60">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A5" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="35">
+        <v>62.8</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="60">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A6" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A4" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="35">
-        <v>6.3</v>
-      </c>
-      <c r="D4" s="35">
-        <v>5</v>
-      </c>
-      <c r="E4" s="35">
-        <v>4.3</v>
-      </c>
-      <c r="F4" s="35">
-        <v>3.84</v>
-      </c>
-      <c r="G4" s="35">
-        <v>5.2</v>
-      </c>
-      <c r="H4" s="65">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="29.4" x14ac:dyDescent="0.7">
-      <c r="A5" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="35">
-        <v>49</v>
-      </c>
-      <c r="C5" s="35">
-        <v>45.2</v>
-      </c>
-      <c r="D5" s="35">
-        <v>36</v>
-      </c>
-      <c r="E5" s="35">
-        <v>32</v>
-      </c>
-      <c r="F5" s="35">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="G5" s="35">
-        <v>35.5</v>
-      </c>
-      <c r="H5" s="65">
-        <v>32.200000000000003</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A6" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="35">
+      <c r="F6" s="35">
+        <v>64.3</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="60">
+        <v>69.900000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A7" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="35">
+        <v>40</v>
+      </c>
+      <c r="C7" s="35">
+        <v>48</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="35">
+        <v>63.5</v>
+      </c>
+      <c r="G7" s="35"/>
+      <c r="H7" s="60">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="52.8" x14ac:dyDescent="0.7">
+      <c r="A8" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35">
         <v>2.93</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D8" s="35">
         <v>2.4</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E8" s="35">
         <v>2.77</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F8" s="35">
         <v>2.77</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G8" s="35">
         <v>2.77</v>
       </c>
-      <c r="H6" s="65">
+      <c r="H8" s="60">
         <v>3.1</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A7" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="35">
-        <v>62.8</v>
-      </c>
-      <c r="G7" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" s="65">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A8" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="35">
-        <v>64.3</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="H8" s="65">
-        <v>69.900000000000006</v>
-      </c>
-    </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A9" s="40" t="s">
-        <v>76</v>
+      <c r="A9" s="36" t="s">
+        <v>110</v>
       </c>
       <c r="B9" s="35">
-        <v>40</v>
+        <v>16.190000000000001</v>
       </c>
       <c r="C9" s="35">
-        <v>48</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>45</v>
+        <v>17.7</v>
+      </c>
+      <c r="D9" s="35">
+        <v>17</v>
+      </c>
+      <c r="E9" s="35">
+        <v>16.399999999999999</v>
       </c>
       <c r="F9" s="35">
-        <v>63.5</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="65">
-        <v>68.900000000000006</v>
+        <v>16</v>
+      </c>
+      <c r="G9" s="35">
+        <v>14.1</v>
+      </c>
+      <c r="H9" s="60">
+        <v>14.2</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A10" s="36" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="35">
-        <v>16.190000000000001</v>
-      </c>
-      <c r="C10" s="35">
-        <v>17.7</v>
-      </c>
-      <c r="D10" s="35">
-        <v>17</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
       <c r="E10" s="35">
-        <v>16.399999999999999</v>
+        <v>16.8</v>
       </c>
       <c r="F10" s="35">
-        <v>16</v>
+        <v>17.100000000000001</v>
       </c>
       <c r="G10" s="35">
-        <v>14.1</v>
-      </c>
-      <c r="H10" s="65">
-        <v>14.2</v>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="H10" s="60">
+        <v>16.5232614249534</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A11" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>44</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
       <c r="E11" s="35">
-        <v>16.8</v>
+        <v>28.4</v>
       </c>
       <c r="F11" s="35">
-        <v>17.100000000000001</v>
+        <v>28.9</v>
       </c>
       <c r="G11" s="35">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="H11" s="65">
-        <v>16.5232614249534</v>
+        <v>30.2</v>
+      </c>
+      <c r="H11" s="60">
+        <v>27.684428243840099</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A12" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>44</v>
+        <v>113</v>
+      </c>
+      <c r="B12" s="35">
+        <v>43.97</v>
+      </c>
+      <c r="C12" s="35">
+        <v>44.3</v>
+      </c>
+      <c r="D12" s="35">
+        <v>43.5</v>
       </c>
       <c r="E12" s="35">
-        <v>28.4</v>
+        <v>44.2</v>
       </c>
       <c r="F12" s="35">
-        <v>28.9</v>
+        <v>43.4</v>
       </c>
       <c r="G12" s="35">
-        <v>30.2</v>
-      </c>
-      <c r="H12" s="65">
-        <v>27.684428243840099</v>
+        <v>41.7</v>
+      </c>
+      <c r="H12" s="60">
+        <v>41.531227347348697</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A13" s="36" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="B13" s="35">
-        <v>43.97</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="C13" s="35">
-        <v>44.3</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D13" s="35">
-        <v>43.5</v>
+        <v>0.7944444444444444</v>
       </c>
       <c r="E13" s="35">
-        <v>44.2</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="F13" s="35">
-        <v>43.4</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="G13" s="35">
-        <v>41.7</v>
-      </c>
-      <c r="H13" s="65">
-        <v>41.531227347348697</v>
+        <v>19.8</v>
+      </c>
+      <c r="H13" s="60">
+        <v>19.961745925589099</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A14" s="36" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="B14" s="35">
-        <v>18.600000000000001</v>
+        <v>50.2</v>
       </c>
       <c r="C14" s="35">
-        <v>18.899999999999999</v>
+        <v>49.6</v>
       </c>
       <c r="D14" s="35">
-        <v>0.7944444444444444</v>
+        <v>50.9</v>
       </c>
       <c r="E14" s="35">
-        <v>18.899999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="F14" s="35">
-        <v>19.100000000000001</v>
+        <v>50.9</v>
       </c>
       <c r="G14" s="35">
-        <v>19.8</v>
-      </c>
-      <c r="H14" s="65">
-        <v>19.961745925589099</v>
+        <v>50.7</v>
+      </c>
+      <c r="H14" s="60">
+        <v>52.117620361244697</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.7">
       <c r="A15" s="36" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B15" s="35">
-        <v>50.2</v>
+        <v>3.8</v>
       </c>
       <c r="C15" s="35">
-        <v>49.6</v>
+        <v>4</v>
       </c>
       <c r="D15" s="35">
-        <v>50.9</v>
+        <v>3.6</v>
       </c>
       <c r="E15" s="35">
-        <v>50.2</v>
+        <v>3.8</v>
       </c>
       <c r="F15" s="35">
-        <v>50.9</v>
+        <v>3.7</v>
       </c>
       <c r="G15" s="35">
-        <v>50.7</v>
-      </c>
-      <c r="H15" s="65">
-        <v>52.117620361244697</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.7">
+        <v>3.6</v>
+      </c>
+      <c r="H15" s="60">
+        <v>4.1568131864506404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="52.8" x14ac:dyDescent="0.7">
       <c r="A16" s="36" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B16" s="35">
-        <v>3.8</v>
+        <v>44</v>
       </c>
       <c r="C16" s="35">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D16" s="35">
-        <v>3.6</v>
+        <v>48</v>
       </c>
       <c r="E16" s="35">
-        <v>3.8</v>
+        <v>46</v>
       </c>
       <c r="F16" s="35">
-        <v>3.7</v>
+        <v>47</v>
       </c>
       <c r="G16" s="35">
-        <v>3.6</v>
-      </c>
-      <c r="H16" s="65">
-        <v>4.1568131864506404</v>
+        <v>48.5</v>
+      </c>
+      <c r="H16" s="60">
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A17" s="36" t="s">
-        <v>103</v>
-      </c>
-      <c r="B17" s="35">
-        <v>44</v>
-      </c>
-      <c r="C17" s="35">
-        <v>45</v>
-      </c>
-      <c r="D17" s="35">
-        <v>48</v>
-      </c>
-      <c r="E17" s="35">
-        <v>46</v>
-      </c>
-      <c r="F17" s="35">
-        <v>47</v>
-      </c>
-      <c r="G17" s="35">
-        <v>48.5</v>
-      </c>
-      <c r="H17" s="65">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A18" s="33" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="55"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
+      <c r="A17" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4361,39 +4367,39 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="28.5546875" style="32" customWidth="1"/>
-    <col min="2" max="3" width="17.5546875" style="45" customWidth="1"/>
+    <col min="2" max="3" width="17.5546875" style="40" customWidth="1"/>
     <col min="4" max="5" width="17.5546875" style="32" customWidth="1"/>
     <col min="6" max="16384" width="11.44140625" style="32"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.95" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="48" t="s">
-        <v>96</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
+      <c r="A1" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A2" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="47">
+      <c r="A2" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="42">
         <v>2000</v>
       </c>
-      <c r="C2" s="47">
+      <c r="C2" s="42">
         <v>2013</v>
       </c>
-      <c r="D2" s="47">
+      <c r="D2" s="42">
         <v>2019</v>
       </c>
-      <c r="E2" s="47">
+      <c r="E2" s="42">
         <v>2023</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A3" s="41" t="s">
+      <c r="A3" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="35">
@@ -4410,8 +4416,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A4" s="46" t="s">
-        <v>15</v>
+      <c r="A4" s="41" t="s">
+        <v>13</v>
       </c>
       <c r="B4" s="34">
         <v>5.0999999999999996</v>
@@ -4427,8 +4433,8 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A5" s="46" t="s">
-        <v>14</v>
+      <c r="A5" s="41" t="s">
+        <v>12</v>
       </c>
       <c r="B5" s="34">
         <v>4.7</v>
@@ -4444,8 +4450,8 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A6" s="46" t="s">
-        <v>13</v>
+      <c r="A6" s="41" t="s">
+        <v>11</v>
       </c>
       <c r="B6" s="34">
         <v>4.9000000000000004</v>
@@ -4461,8 +4467,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A7" s="46" t="s">
-        <v>12</v>
+      <c r="A7" s="41" t="s">
+        <v>10</v>
       </c>
       <c r="B7" s="34">
         <v>5.6</v>
@@ -4478,8 +4484,8 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A8" s="46" t="s">
-        <v>11</v>
+      <c r="A8" s="41" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="34">
         <v>4.8</v>
@@ -4495,8 +4501,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A9" s="46" t="s">
-        <v>10</v>
+      <c r="A9" s="41" t="s">
+        <v>8</v>
       </c>
       <c r="B9" s="34">
         <v>4.7</v>
@@ -4512,8 +4518,8 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A10" s="46" t="s">
-        <v>9</v>
+      <c r="A10" s="41" t="s">
+        <v>7</v>
       </c>
       <c r="B10" s="34">
         <v>4.3</v>
@@ -4529,8 +4535,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A11" s="46" t="s">
-        <v>51</v>
+      <c r="A11" s="41" t="s">
+        <v>48</v>
       </c>
       <c r="B11" s="35">
         <v>5</v>
@@ -4546,8 +4552,8 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A12" s="46" t="s">
-        <v>8</v>
+      <c r="A12" s="41" t="s">
+        <v>6</v>
       </c>
       <c r="B12" s="34">
         <v>4.2</v>
@@ -4563,8 +4569,8 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A13" s="46" t="s">
-        <v>70</v>
+      <c r="A13" s="41" t="s">
+        <v>60</v>
       </c>
       <c r="B13" s="34">
         <v>6.5</v>
@@ -4580,8 +4586,8 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A14" s="46" t="s">
-        <v>7</v>
+      <c r="A14" s="41" t="s">
+        <v>5</v>
       </c>
       <c r="B14" s="34">
         <v>4.3</v>
@@ -4597,8 +4603,8 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A15" s="46" t="s">
-        <v>6</v>
+      <c r="A15" s="41" t="s">
+        <v>4</v>
       </c>
       <c r="B15" s="34">
         <v>3.7</v>
@@ -4614,8 +4620,8 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A16" s="46" t="s">
-        <v>3</v>
+      <c r="A16" s="41" t="s">
+        <v>1</v>
       </c>
       <c r="B16" s="34">
         <v>4.8</v>
@@ -4631,8 +4637,8 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A17" s="84" t="s">
-        <v>71</v>
+      <c r="A17" s="79" t="s">
+        <v>61</v>
       </c>
       <c r="B17" s="34"/>
       <c r="C17" s="34"/>
@@ -4644,8 +4650,8 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A18" s="84" t="s">
-        <v>5</v>
+      <c r="A18" s="79" t="s">
+        <v>3</v>
       </c>
       <c r="B18" s="34"/>
       <c r="C18" s="34"/>
@@ -4657,8 +4663,8 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A19" s="84" t="s">
-        <v>4</v>
+      <c r="A19" s="79" t="s">
+        <v>2</v>
       </c>
       <c r="B19" s="34"/>
       <c r="C19" s="34"/>
@@ -4670,8 +4676,8 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A20" s="83" t="s">
-        <v>105</v>
+      <c r="A20" s="78" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees/Statistiques Démographiques et sociales/Démographie/Demographique_Portail.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Démographie/Demographique_Portail.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Démographie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1430973-F411-46FC-8EE1-76767237B3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3369E8CD-EF58-45A5-AEE5-A240D1492EDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="512" activeTab="7" xr2:uid="{AB8ECA8C-A6C4-4626-BABF-82DEB90B841C}"/>
   </bookViews>
@@ -16,12 +16,12 @@
     <sheet name="T1.1" sheetId="1" r:id="rId1"/>
     <sheet name="T1.2" sheetId="2" r:id="rId2"/>
     <sheet name="T1.3" sheetId="3" r:id="rId3"/>
-    <sheet name="T1.4" sheetId="4" r:id="rId4"/>
-    <sheet name="T1.5" sheetId="5" r:id="rId5"/>
-    <sheet name="T1.5bis" sheetId="9" r:id="rId6"/>
-    <sheet name="T1.5bis1" sheetId="8" r:id="rId7"/>
-    <sheet name="T1.6" sheetId="6" r:id="rId8"/>
-    <sheet name="T1.7" sheetId="7" r:id="rId9"/>
+    <sheet name="T1.5" sheetId="5" r:id="rId4"/>
+    <sheet name="T1.5bis" sheetId="9" r:id="rId5"/>
+    <sheet name="T1.5bis1" sheetId="8" r:id="rId6"/>
+    <sheet name="T1.6" sheetId="6" r:id="rId7"/>
+    <sheet name="T1.7" sheetId="7" r:id="rId8"/>
+    <sheet name="T1.8" sheetId="4" r:id="rId9"/>
   </sheets>
   <externalReferences>
     <externalReference r:id="rId10"/>
@@ -215,19 +215,10 @@
     <t xml:space="preserve">                               Total</t>
   </si>
   <si>
-    <t>Tableau 1.1: Répartition de la population selon le milieu de résidence et le sexe; 1977 - 2027</t>
-  </si>
-  <si>
     <t>Guidimakha</t>
   </si>
   <si>
     <t>Nouakchott-Ouest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableau 1.2 : Evolution de la population par Wilaya; 1977- 2027 </t>
-  </si>
-  <si>
-    <t>Tableau 1. 3 : Evolution de la population par groupe d'âge; 1977 - 2027</t>
   </si>
   <si>
     <t>Mortalité~Espérance de vie des hommes (en an)</t>
@@ -257,9 +248,6 @@
     <t xml:space="preserve">2023~Ensemble  </t>
   </si>
   <si>
-    <t>Tableau 1.4 : Evolution du quotient de mortalité dans l’enfance selon le sexe (en ‰), 2000 - 2023</t>
-  </si>
-  <si>
     <t>65 ans et plus</t>
   </si>
   <si>
@@ -281,33 +269,6 @@
     <t xml:space="preserve">2023~Garçons  </t>
   </si>
   <si>
-    <t>Tableau 1.6: Répartition de la population par groupe d'âge selon le sexe, en 2023</t>
-  </si>
-  <si>
-    <t>Tableau 1.7: Répartition de la population par grands groupes d'âge selon le sexe, en 2023</t>
-  </si>
-  <si>
-    <t>Tableau 1.9 : Evolution de l'Indice synthétique de fécondité par Wilaya; 2000 - 2023</t>
-  </si>
-  <si>
-    <t>Source : ANSADE, RGPH 1977-2023 et Projections démographiques 2024</t>
-  </si>
-  <si>
-    <t>Source : ANSADE, RGPH 2000-2023 et EDSM 2019-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source : ANSADE, RGPH 2023 </t>
-  </si>
-  <si>
-    <t>Tableau 1.5: Répartition(en %) de la population par groupe d'âge selon le sexe, en 2023</t>
-  </si>
-  <si>
-    <t>Tableau 1.8 : Principales caractéristiques démographiques de la population; 1977  2023</t>
-  </si>
-  <si>
-    <t>Source : ANSADE, RGPH 19772023, MICS5 2015 et EDSM 201921</t>
-  </si>
-  <si>
     <t>Mauritanie~Masculine</t>
   </si>
   <si>
@@ -405,6 +366,45 @@
   </si>
   <si>
     <t>Rural~Féminine</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.1: Répartition de la population selon le milieu de résidence et le sexe; 1977 - 2027</t>
+  </si>
+  <si>
+    <t>Source : RGPH/1977-2023 et Projections démographiques 2024</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.2 : Evolution de la population par Wilaya; 1977- 2027</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.3 : Evolution de la population par groupe d'âge; 1977 - 2027</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.4: Répartition(en %) de la population par groupe d'âge selon le sexe, en 2023</t>
+  </si>
+  <si>
+    <t>Source : RGPH/2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.5: Répartition de la population par groupe d'âge selon le sexe, en 2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.6 : Répartition de la population par grands groupes d'âge selon le sexe, en 2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.7 : Principales caractéristiques démographiques de la population; 1977-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.8 : Evolution de l'Indice synthétique de fécondité par Wilaya; 2000 - 2023</t>
+  </si>
+  <si>
+    <t>Source : RGPH/2000-2023 et EDSM/2019</t>
+  </si>
+  <si>
+    <t>Tableau 1.1.9 : Evolution du quotient de mortalité infantile et infanto juvénile selon le sexe (en ‰), 2000 - 2023</t>
+  </si>
+  <si>
+    <t>Source : RGPH/1977-2023, MICS/2015 et EDSM/2019</t>
   </si>
 </sst>
 </file>
@@ -1403,7 +1403,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A1" s="85" t="s">
-        <v>59</v>
+        <v>107</v>
       </c>
       <c r="B1" s="85"/>
       <c r="C1" s="85"/>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A4" s="6" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="B4" s="5">
         <f>B7+B10</f>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A5" s="6" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B5" s="5">
         <f>B8+B11</f>
@@ -1565,7 +1565,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A6" s="4" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="B6" s="3">
         <v>303819</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A7" s="6" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B7" s="5">
         <v>164304</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A8" s="6" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="B8" s="5">
         <v>139515</v>
@@ -1661,7 +1661,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A9" s="4" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3">
         <v>1035011</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A10" s="6" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="B10" s="5">
         <v>494057</v>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A11" s="6" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B11" s="5">
         <v>540954</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A12" s="80" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1788,7 +1788,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="58" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="B1" s="58"/>
       <c r="C1" s="58"/>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A4" s="15" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="B4" s="13">
         <v>156721</v>
@@ -1892,7 +1892,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A5" s="15" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="B5" s="13">
         <v>124194</v>
@@ -1924,7 +1924,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A6" s="15" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="B6" s="13">
         <v>129162</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A7" s="15" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="B7" s="13">
         <v>149432</v>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A8" s="15" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="B8" s="13">
         <v>151353</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A9" s="15" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="B9" s="13">
         <v>216008</v>
@@ -2052,7 +2052,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A10" s="15" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="B10" s="13">
         <v>55354</v>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A11" s="15" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B11" s="13">
         <v>53526</v>
@@ -2116,7 +2116,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A12" s="15" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B12" s="13">
         <v>74980</v>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A13" s="15" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="B13" s="13">
         <v>83231</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A14" s="15" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="B14" s="13">
         <v>22554</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A15" s="15" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B15" s="13">
         <v>17611</v>
@@ -2244,7 +2244,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A16" s="15" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B16" s="13">
         <v>134704</v>
@@ -2281,7 +2281,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A17" s="14" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -2305,7 +2305,7 @@
     </row>
     <row r="18" spans="1:10" ht="30.6" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A18" s="14" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -2329,7 +2329,7 @@
     </row>
     <row r="19" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A19" s="14" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -2353,7 +2353,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A20" s="80" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="F20" s="47"/>
     </row>
@@ -2378,7 +2378,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="25" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.85">
       <c r="A20" s="80" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="F20" s="17"/>
       <c r="G20" s="17"/>
@@ -2986,6 +2986,1476 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D797ADB-8B79-43C8-BFBB-5BCFDD0E1709}">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
+  <cols>
+    <col min="1" max="1" width="30.88671875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
+    <col min="5" max="16384" width="11.5546875" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="A1" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+    </row>
+    <row r="2" spans="1:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
+      <c r="A2" s="45" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="67">
+        <v>1</v>
+      </c>
+      <c r="C3" s="67">
+        <v>1</v>
+      </c>
+      <c r="D3" s="67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="68">
+        <v>0.15019773378675499</v>
+      </c>
+      <c r="C4" s="68">
+        <v>0.1352497941416286</v>
+      </c>
+      <c r="D4" s="68">
+        <v>0.14245591469258082</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="68">
+        <v>0.14653420973582504</v>
+      </c>
+      <c r="C5" s="68">
+        <v>0.13394503770824412</v>
+      </c>
+      <c r="D5" s="68">
+        <v>0.14001404075614515</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="68">
+        <v>0.13739234976245948</v>
+      </c>
+      <c r="C6" s="68">
+        <v>0.12860712771846924</v>
+      </c>
+      <c r="D6" s="68">
+        <v>0.13284231802581759</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="68">
+        <v>0.11496828521397703</v>
+      </c>
+      <c r="C7" s="68">
+        <v>0.11361249162304529</v>
+      </c>
+      <c r="D7" s="68">
+        <v>0.11426609421129681</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="68">
+        <v>7.9665661184978614E-2</v>
+      </c>
+      <c r="C8" s="68">
+        <v>9.0643644153031014E-2</v>
+      </c>
+      <c r="D8" s="68">
+        <v>8.5351365044156691E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="68">
+        <v>6.4186013214147894E-2</v>
+      </c>
+      <c r="C9" s="68">
+        <v>7.6698085181093917E-2</v>
+      </c>
+      <c r="D9" s="68">
+        <v>7.0666250620934734E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="68">
+        <v>5.591810465081945E-2</v>
+      </c>
+      <c r="C10" s="68">
+        <v>6.5754475814841201E-2</v>
+      </c>
+      <c r="D10" s="68">
+        <v>6.1012546285096246E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="68">
+        <v>4.8336952175404693E-2</v>
+      </c>
+      <c r="C11" s="68">
+        <v>5.5188342892053432E-2</v>
+      </c>
+      <c r="D11" s="68">
+        <v>5.1885416292610474E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="68">
+        <v>4.1175387640228434E-2</v>
+      </c>
+      <c r="C12" s="68">
+        <v>4.3573113700768253E-2</v>
+      </c>
+      <c r="D12" s="68">
+        <v>4.2417215064534643E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="68">
+        <v>3.59976668738025E-2</v>
+      </c>
+      <c r="C13" s="68">
+        <v>3.66268739322008E-2</v>
+      </c>
+      <c r="D13" s="68">
+        <v>3.6323545043498134E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="68">
+        <v>3.1990881120045618E-2</v>
+      </c>
+      <c r="C14" s="68">
+        <v>3.2262922638433389E-2</v>
+      </c>
+      <c r="D14" s="68">
+        <v>3.2131776538772014E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="68">
+        <v>2.744503612546377E-2</v>
+      </c>
+      <c r="C15" s="68">
+        <v>2.6821305902556256E-2</v>
+      </c>
+      <c r="D15" s="68">
+        <v>2.7121994511212125E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="68">
+        <v>2.2813682775715161E-2</v>
+      </c>
+      <c r="C16" s="68">
+        <v>2.1133319518059718E-2</v>
+      </c>
+      <c r="D16" s="68">
+        <v>2.1943391038872315E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="68">
+        <v>1.7500329239129826E-2</v>
+      </c>
+      <c r="C17" s="68">
+        <v>1.5802583138069613E-2</v>
+      </c>
+      <c r="D17" s="68">
+        <v>1.6621034600840572E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="68">
+        <v>1.1843244518614555E-2</v>
+      </c>
+      <c r="C18" s="68">
+        <v>1.0541807658724582E-2</v>
+      </c>
+      <c r="D18" s="68">
+        <v>1.1169205890429929E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="68">
+        <v>5.943293015444771E-3</v>
+      </c>
+      <c r="C19" s="68">
+        <v>5.4016342906763716E-3</v>
+      </c>
+      <c r="D19" s="68">
+        <v>5.662757773934708E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="68">
+        <v>8.0911689664886523E-3</v>
+      </c>
+      <c r="C20" s="68">
+        <v>8.1374399890821528E-3</v>
+      </c>
+      <c r="D20" s="68">
+        <v>8.1151335992914707E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A21" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="B24" s="70"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D496BD-5EF2-4B45-BA1D-4C8409593D31}">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
+  <cols>
+    <col min="1" max="1" width="30.88671875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
+    <col min="5" max="16384" width="11.5546875" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A1" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+    </row>
+    <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.85">
+      <c r="A2" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A3" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="74">
+        <v>2375470</v>
+      </c>
+      <c r="C3" s="74">
+        <v>2552062</v>
+      </c>
+      <c r="D3" s="74">
+        <v>4927532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A4" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="72">
+        <v>356790</v>
+      </c>
+      <c r="C4" s="72">
+        <v>345166</v>
+      </c>
+      <c r="D4" s="72">
+        <v>701956</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="72">
+        <v>348088</v>
+      </c>
+      <c r="C5" s="72">
+        <v>341836</v>
+      </c>
+      <c r="D5" s="72">
+        <v>689924</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="72">
+        <v>326371</v>
+      </c>
+      <c r="C6" s="72">
+        <v>328214</v>
+      </c>
+      <c r="D6" s="72">
+        <v>654585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="72">
+        <v>273104</v>
+      </c>
+      <c r="C7" s="72">
+        <v>289946</v>
+      </c>
+      <c r="D7" s="72">
+        <v>563050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="72">
+        <v>189243</v>
+      </c>
+      <c r="C8" s="72">
+        <v>231328</v>
+      </c>
+      <c r="D8" s="72">
+        <v>420572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="72">
+        <v>152472</v>
+      </c>
+      <c r="C9" s="72">
+        <v>195738</v>
+      </c>
+      <c r="D9" s="72">
+        <v>348210</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A10" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="72">
+        <v>132832</v>
+      </c>
+      <c r="C10" s="72">
+        <v>167809</v>
+      </c>
+      <c r="D10" s="72">
+        <v>300641</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="72">
+        <v>114823</v>
+      </c>
+      <c r="C11" s="72">
+        <v>140844</v>
+      </c>
+      <c r="D11" s="72">
+        <v>255667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="72">
+        <v>97811</v>
+      </c>
+      <c r="C12" s="72">
+        <v>111201</v>
+      </c>
+      <c r="D12" s="72">
+        <v>209012</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A13" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="72">
+        <v>85511</v>
+      </c>
+      <c r="C13" s="72">
+        <v>93474</v>
+      </c>
+      <c r="D13" s="72">
+        <v>178985</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="72">
+        <v>75993</v>
+      </c>
+      <c r="C14" s="72">
+        <v>82337</v>
+      </c>
+      <c r="D14" s="72">
+        <v>158330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A15" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="72">
+        <v>65195</v>
+      </c>
+      <c r="C15" s="72">
+        <v>68450</v>
+      </c>
+      <c r="D15" s="72">
+        <v>133645</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" s="72">
+        <v>54193</v>
+      </c>
+      <c r="C16" s="72">
+        <v>53934</v>
+      </c>
+      <c r="D16" s="72">
+        <v>108127</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="72">
+        <v>41572</v>
+      </c>
+      <c r="C17" s="72">
+        <v>40329</v>
+      </c>
+      <c r="D17" s="72">
+        <v>81901</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A18" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="72">
+        <v>28133</v>
+      </c>
+      <c r="C18" s="72">
+        <v>26903</v>
+      </c>
+      <c r="D18" s="72">
+        <v>55037</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" s="72">
+        <v>14118</v>
+      </c>
+      <c r="C19" s="72">
+        <v>13785</v>
+      </c>
+      <c r="D19" s="72">
+        <v>27903</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="72">
+        <v>19220</v>
+      </c>
+      <c r="C20" s="72">
+        <v>20767</v>
+      </c>
+      <c r="D20" s="72">
+        <v>39988</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="A21" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.85">
+      <c r="B24" s="70"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEF1C8E-D6B9-4367-97B0-BA0B367D0AD5}">
+  <dimension ref="A1:O10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
+  <cols>
+    <col min="1" max="1" width="24" style="29" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
+    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="29"/>
+    <col min="6" max="8" width="15.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="11.5546875" style="29"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A1" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+    </row>
+    <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.85">
+      <c r="A2" s="71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="66" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="66" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="66" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="76" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="75" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="74">
+        <v>2375470</v>
+      </c>
+      <c r="C3" s="74">
+        <v>2552062</v>
+      </c>
+      <c r="D3" s="74">
+        <v>4927532</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A4" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="72">
+        <v>1031249</v>
+      </c>
+      <c r="C4" s="72">
+        <v>1015215</v>
+      </c>
+      <c r="D4" s="72">
+        <v>2046465</v>
+      </c>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" s="72">
+        <v>1241178</v>
+      </c>
+      <c r="C5" s="72">
+        <v>1435061</v>
+      </c>
+      <c r="D5" s="72">
+        <v>2676239</v>
+      </c>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="72">
+        <v>103043</v>
+      </c>
+      <c r="C6" s="72">
+        <v>101785</v>
+      </c>
+      <c r="D6" s="72">
+        <v>204828</v>
+      </c>
+      <c r="F6" s="77"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="A7" s="16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.85">
+      <c r="B10" s="70"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12B744F-6F17-4891-BC34-B3B89A801878}">
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="97.88671875" style="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="8" width="16.44140625" style="32" customWidth="1"/>
+    <col min="9" max="9" width="18.6640625" style="32" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" style="32" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="39"/>
+    </row>
+    <row r="2" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.75">
+      <c r="A2" s="84"/>
+      <c r="B2" s="83">
+        <v>1977</v>
+      </c>
+      <c r="C2" s="83">
+        <v>1988</v>
+      </c>
+      <c r="D2" s="83">
+        <v>2000</v>
+      </c>
+      <c r="E2" s="83">
+        <v>2013</v>
+      </c>
+      <c r="F2" s="83">
+        <v>2015</v>
+      </c>
+      <c r="G2" s="83">
+        <v>2019</v>
+      </c>
+      <c r="H2" s="83">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="27" thickTop="1" x14ac:dyDescent="0.7">
+      <c r="A3" s="36" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35">
+        <v>6.3</v>
+      </c>
+      <c r="D3" s="35">
+        <v>5</v>
+      </c>
+      <c r="E3" s="35">
+        <v>4.3</v>
+      </c>
+      <c r="F3" s="35">
+        <v>3.84</v>
+      </c>
+      <c r="G3" s="35">
+        <v>5.2</v>
+      </c>
+      <c r="H3" s="60">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="29.4" x14ac:dyDescent="0.7">
+      <c r="A4" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="B4" s="35">
+        <v>49</v>
+      </c>
+      <c r="C4" s="35">
+        <v>45.2</v>
+      </c>
+      <c r="D4" s="35">
+        <v>36</v>
+      </c>
+      <c r="E4" s="35">
+        <v>32</v>
+      </c>
+      <c r="F4" s="35">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="G4" s="35">
+        <v>35.5</v>
+      </c>
+      <c r="H4" s="60">
+        <v>32.200000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A5" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="35">
+        <v>62.8</v>
+      </c>
+      <c r="G5" s="35"/>
+      <c r="H5" s="60">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A6" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="35"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="35">
+        <v>64.3</v>
+      </c>
+      <c r="G6" s="35"/>
+      <c r="H6" s="60">
+        <v>69.900000000000006</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A7" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" s="35">
+        <v>40</v>
+      </c>
+      <c r="C7" s="35">
+        <v>48</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="35">
+        <v>63.5</v>
+      </c>
+      <c r="G7" s="35"/>
+      <c r="H7" s="60">
+        <v>68.900000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A8" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35">
+        <v>2.93</v>
+      </c>
+      <c r="D8" s="35">
+        <v>2.4</v>
+      </c>
+      <c r="E8" s="35">
+        <v>2.77</v>
+      </c>
+      <c r="F8" s="35">
+        <v>2.77</v>
+      </c>
+      <c r="G8" s="35">
+        <v>2.77</v>
+      </c>
+      <c r="H8" s="60">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A9" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B9" s="35">
+        <v>16.190000000000001</v>
+      </c>
+      <c r="C9" s="35">
+        <v>17.7</v>
+      </c>
+      <c r="D9" s="35">
+        <v>17</v>
+      </c>
+      <c r="E9" s="35">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="F9" s="35">
+        <v>16</v>
+      </c>
+      <c r="G9" s="35">
+        <v>14.1</v>
+      </c>
+      <c r="H9" s="60">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A10" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="35"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35">
+        <v>16.8</v>
+      </c>
+      <c r="F10" s="35">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="G10" s="35">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="H10" s="60">
+        <v>16.5232614249534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A11" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B11" s="35"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35">
+        <v>28.4</v>
+      </c>
+      <c r="F11" s="35">
+        <v>28.9</v>
+      </c>
+      <c r="G11" s="35">
+        <v>30.2</v>
+      </c>
+      <c r="H11" s="60">
+        <v>27.684428243840099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A12" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B12" s="35">
+        <v>43.97</v>
+      </c>
+      <c r="C12" s="35">
+        <v>44.3</v>
+      </c>
+      <c r="D12" s="35">
+        <v>43.5</v>
+      </c>
+      <c r="E12" s="35">
+        <v>44.2</v>
+      </c>
+      <c r="F12" s="35">
+        <v>43.4</v>
+      </c>
+      <c r="G12" s="35">
+        <v>41.7</v>
+      </c>
+      <c r="H12" s="60">
+        <v>41.531227347348697</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A13" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="35">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="C13" s="35">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D13" s="35">
+        <v>0.7944444444444444</v>
+      </c>
+      <c r="E13" s="35">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="F13" s="35">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="G13" s="35">
+        <v>19.8</v>
+      </c>
+      <c r="H13" s="60">
+        <v>19.961745925589099</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A14" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" s="35">
+        <v>50.2</v>
+      </c>
+      <c r="C14" s="35">
+        <v>49.6</v>
+      </c>
+      <c r="D14" s="35">
+        <v>50.9</v>
+      </c>
+      <c r="E14" s="35">
+        <v>50.2</v>
+      </c>
+      <c r="F14" s="35">
+        <v>50.9</v>
+      </c>
+      <c r="G14" s="35">
+        <v>50.7</v>
+      </c>
+      <c r="H14" s="60">
+        <v>52.117620361244697</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A15" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B15" s="35">
+        <v>3.8</v>
+      </c>
+      <c r="C15" s="35">
+        <v>4</v>
+      </c>
+      <c r="D15" s="35">
+        <v>3.6</v>
+      </c>
+      <c r="E15" s="35">
+        <v>3.8</v>
+      </c>
+      <c r="F15" s="35">
+        <v>3.7</v>
+      </c>
+      <c r="G15" s="35">
+        <v>3.6</v>
+      </c>
+      <c r="H15" s="60">
+        <v>4.1568131864506404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A16" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="35">
+        <v>44</v>
+      </c>
+      <c r="C16" s="35">
+        <v>45</v>
+      </c>
+      <c r="D16" s="35">
+        <v>48</v>
+      </c>
+      <c r="E16" s="35">
+        <v>46</v>
+      </c>
+      <c r="F16" s="35">
+        <v>47</v>
+      </c>
+      <c r="G16" s="35">
+        <v>48.5</v>
+      </c>
+      <c r="H16" s="60">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.7">
+      <c r="A17" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B17" s="49"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26305625-B393-4676-885C-66F897A4EF8D}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
+  <cols>
+    <col min="1" max="1" width="28.5546875" style="32" customWidth="1"/>
+    <col min="2" max="3" width="17.5546875" style="40" customWidth="1"/>
+    <col min="4" max="5" width="17.5546875" style="32" customWidth="1"/>
+    <col min="6" max="16384" width="11.44140625" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="28.95" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A1" s="43" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A2" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="42">
+        <v>2000</v>
+      </c>
+      <c r="C2" s="42">
+        <v>2013</v>
+      </c>
+      <c r="D2" s="42">
+        <v>2019</v>
+      </c>
+      <c r="E2" s="42">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A3" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="35">
+        <v>5</v>
+      </c>
+      <c r="C3" s="34">
+        <v>4.3</v>
+      </c>
+      <c r="D3" s="34">
+        <v>5.2</v>
+      </c>
+      <c r="E3" s="34">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A4" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="34">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="C4" s="34">
+        <v>4.8</v>
+      </c>
+      <c r="D4" s="34">
+        <v>6.3</v>
+      </c>
+      <c r="E4" s="34">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A5" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="34">
+        <v>4.7</v>
+      </c>
+      <c r="C5" s="34">
+        <v>4.2</v>
+      </c>
+      <c r="D5" s="34">
+        <v>6.1</v>
+      </c>
+      <c r="E5" s="34">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A6" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="34">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C6" s="34">
+        <v>4.3</v>
+      </c>
+      <c r="D6" s="34">
+        <v>5.7</v>
+      </c>
+      <c r="E6" s="34">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A7" s="41" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="34">
+        <v>5.6</v>
+      </c>
+      <c r="C7" s="34">
+        <v>5</v>
+      </c>
+      <c r="D7" s="35">
+        <v>6</v>
+      </c>
+      <c r="E7" s="35">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A8" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="34">
+        <v>4.8</v>
+      </c>
+      <c r="C8" s="34">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D8" s="35">
+        <v>6</v>
+      </c>
+      <c r="E8" s="35">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A9" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="34">
+        <v>4.7</v>
+      </c>
+      <c r="C9" s="34">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D9" s="34">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E9" s="34">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A10" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="34">
+        <v>4.3</v>
+      </c>
+      <c r="C10" s="34">
+        <v>3.8</v>
+      </c>
+      <c r="D10" s="34">
+        <v>4.2</v>
+      </c>
+      <c r="E10" s="35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A11" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="35">
+        <v>5</v>
+      </c>
+      <c r="C11" s="34">
+        <v>3.9</v>
+      </c>
+      <c r="D11" s="34">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E11" s="34">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A12" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="34">
+        <v>4.2</v>
+      </c>
+      <c r="C12" s="34">
+        <v>3.9</v>
+      </c>
+      <c r="D12" s="35">
+        <v>6</v>
+      </c>
+      <c r="E12" s="35">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A13" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="34">
+        <v>6.5</v>
+      </c>
+      <c r="C13" s="34">
+        <v>5.9</v>
+      </c>
+      <c r="D13" s="34">
+        <v>6.5</v>
+      </c>
+      <c r="E13" s="34">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A14" s="41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="34">
+        <v>4.3</v>
+      </c>
+      <c r="C14" s="34">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D14" s="34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E14" s="35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A15" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="34">
+        <v>3.7</v>
+      </c>
+      <c r="C15" s="34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D15" s="34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E15" s="34">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A16" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="34">
+        <v>4.8</v>
+      </c>
+      <c r="C16" s="34">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D16" s="34">
+        <v>3.9</v>
+      </c>
+      <c r="E16" s="34">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A17" s="79" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35">
+        <v>4</v>
+      </c>
+      <c r="E17" s="34">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A18" s="79" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34">
+        <v>3.9</v>
+      </c>
+      <c r="E18" s="34">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A19" s="79" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34">
+        <v>3.8</v>
+      </c>
+      <c r="E19" s="34">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.7">
+      <c r="A20" s="78" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1420C94C-703C-419F-8671-A6C8B4F72455}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
@@ -3010,7 +4480,7 @@
   <sheetData>
     <row r="1" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.85">
       <c r="A1" s="25" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -3026,7 +4496,7 @@
         <v>50</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>51</v>
@@ -3035,7 +4505,7 @@
         <v>52</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G2" s="44" t="s">
         <v>53</v>
@@ -3044,19 +4514,19 @@
         <v>54</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="J2" s="44" t="s">
         <v>55</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.85">
@@ -3186,7 +4656,7 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.85">
       <c r="A6" s="46" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.85">
@@ -3214,1474 +4684,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D797ADB-8B79-43C8-BFBB-5BCFDD0E1709}">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
-  <cols>
-    <col min="1" max="1" width="30.88671875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
-    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
-    <col min="5" max="16384" width="11.5546875" style="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="33" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A1" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-    </row>
-    <row r="2" spans="1:15" ht="26.4" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A2" s="45" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="67">
-        <v>1</v>
-      </c>
-      <c r="C3" s="67">
-        <v>1</v>
-      </c>
-      <c r="D3" s="67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="68">
-        <v>0.15019773378675499</v>
-      </c>
-      <c r="C4" s="68">
-        <v>0.1352497941416286</v>
-      </c>
-      <c r="D4" s="68">
-        <v>0.14245591469258082</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="68">
-        <v>0.14653420973582504</v>
-      </c>
-      <c r="C5" s="68">
-        <v>0.13394503770824412</v>
-      </c>
-      <c r="D5" s="68">
-        <v>0.14001404075614515</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="68">
-        <v>0.13739234976245948</v>
-      </c>
-      <c r="C6" s="68">
-        <v>0.12860712771846924</v>
-      </c>
-      <c r="D6" s="68">
-        <v>0.13284231802581759</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="68">
-        <v>0.11496828521397703</v>
-      </c>
-      <c r="C7" s="68">
-        <v>0.11361249162304529</v>
-      </c>
-      <c r="D7" s="68">
-        <v>0.11426609421129681</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="68">
-        <v>7.9665661184978614E-2</v>
-      </c>
-      <c r="C8" s="68">
-        <v>9.0643644153031014E-2</v>
-      </c>
-      <c r="D8" s="68">
-        <v>8.5351365044156691E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="68">
-        <v>6.4186013214147894E-2</v>
-      </c>
-      <c r="C9" s="68">
-        <v>7.6698085181093917E-2</v>
-      </c>
-      <c r="D9" s="68">
-        <v>7.0666250620934734E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="68">
-        <v>5.591810465081945E-2</v>
-      </c>
-      <c r="C10" s="68">
-        <v>6.5754475814841201E-2</v>
-      </c>
-      <c r="D10" s="68">
-        <v>6.1012546285096246E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="68">
-        <v>4.8336952175404693E-2</v>
-      </c>
-      <c r="C11" s="68">
-        <v>5.5188342892053432E-2</v>
-      </c>
-      <c r="D11" s="68">
-        <v>5.1885416292610474E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="68">
-        <v>4.1175387640228434E-2</v>
-      </c>
-      <c r="C12" s="68">
-        <v>4.3573113700768253E-2</v>
-      </c>
-      <c r="D12" s="68">
-        <v>4.2417215064534643E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="68">
-        <v>3.59976668738025E-2</v>
-      </c>
-      <c r="C13" s="68">
-        <v>3.66268739322008E-2</v>
-      </c>
-      <c r="D13" s="68">
-        <v>3.6323545043498134E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="68">
-        <v>3.1990881120045618E-2</v>
-      </c>
-      <c r="C14" s="68">
-        <v>3.2262922638433389E-2</v>
-      </c>
-      <c r="D14" s="68">
-        <v>3.2131776538772014E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="68">
-        <v>2.744503612546377E-2</v>
-      </c>
-      <c r="C15" s="68">
-        <v>2.6821305902556256E-2</v>
-      </c>
-      <c r="D15" s="68">
-        <v>2.7121994511212125E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="68">
-        <v>2.2813682775715161E-2</v>
-      </c>
-      <c r="C16" s="68">
-        <v>2.1133319518059718E-2</v>
-      </c>
-      <c r="D16" s="68">
-        <v>2.1943391038872315E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="68">
-        <v>1.7500329239129826E-2</v>
-      </c>
-      <c r="C17" s="68">
-        <v>1.5802583138069613E-2</v>
-      </c>
-      <c r="D17" s="68">
-        <v>1.6621034600840572E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="68">
-        <v>1.1843244518614555E-2</v>
-      </c>
-      <c r="C18" s="68">
-        <v>1.0541807658724582E-2</v>
-      </c>
-      <c r="D18" s="68">
-        <v>1.1169205890429929E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A19" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="68">
-        <v>5.943293015444771E-3</v>
-      </c>
-      <c r="C19" s="68">
-        <v>5.4016342906763716E-3</v>
-      </c>
-      <c r="D19" s="68">
-        <v>5.662757773934708E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="68">
-        <v>8.0911689664886523E-3</v>
-      </c>
-      <c r="C20" s="68">
-        <v>8.1374399890821528E-3</v>
-      </c>
-      <c r="D20" s="68">
-        <v>8.1151335992914707E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A21" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="B24" s="70"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06D496BD-5EF2-4B45-BA1D-4C8409593D31}">
-  <dimension ref="A1:O24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
-  <cols>
-    <col min="1" max="1" width="30.88671875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
-    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
-    <col min="5" max="16384" width="11.5546875" style="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A1" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-    </row>
-    <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.85">
-      <c r="A2" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A3" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="74">
-        <v>2375470</v>
-      </c>
-      <c r="C3" s="74">
-        <v>2552062</v>
-      </c>
-      <c r="D3" s="74">
-        <v>4927532</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A4" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="72">
-        <v>356790</v>
-      </c>
-      <c r="C4" s="72">
-        <v>345166</v>
-      </c>
-      <c r="D4" s="72">
-        <v>701956</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="72">
-        <v>348088</v>
-      </c>
-      <c r="C5" s="72">
-        <v>341836</v>
-      </c>
-      <c r="D5" s="72">
-        <v>689924</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A6" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="72">
-        <v>326371</v>
-      </c>
-      <c r="C6" s="72">
-        <v>328214</v>
-      </c>
-      <c r="D6" s="72">
-        <v>654585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="72">
-        <v>273104</v>
-      </c>
-      <c r="C7" s="72">
-        <v>289946</v>
-      </c>
-      <c r="D7" s="72">
-        <v>563050</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="72">
-        <v>189243</v>
-      </c>
-      <c r="C8" s="72">
-        <v>231328</v>
-      </c>
-      <c r="D8" s="72">
-        <v>420572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A9" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="72">
-        <v>152472</v>
-      </c>
-      <c r="C9" s="72">
-        <v>195738</v>
-      </c>
-      <c r="D9" s="72">
-        <v>348210</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="72">
-        <v>132832</v>
-      </c>
-      <c r="C10" s="72">
-        <v>167809</v>
-      </c>
-      <c r="D10" s="72">
-        <v>300641</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="72">
-        <v>114823</v>
-      </c>
-      <c r="C11" s="72">
-        <v>140844</v>
-      </c>
-      <c r="D11" s="72">
-        <v>255667</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A12" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="72">
-        <v>97811</v>
-      </c>
-      <c r="C12" s="72">
-        <v>111201</v>
-      </c>
-      <c r="D12" s="72">
-        <v>209012</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A13" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="72">
-        <v>85511</v>
-      </c>
-      <c r="C13" s="72">
-        <v>93474</v>
-      </c>
-      <c r="D13" s="72">
-        <v>178985</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="72">
-        <v>75993</v>
-      </c>
-      <c r="C14" s="72">
-        <v>82337</v>
-      </c>
-      <c r="D14" s="72">
-        <v>158330</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A15" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="72">
-        <v>65195</v>
-      </c>
-      <c r="C15" s="72">
-        <v>68450</v>
-      </c>
-      <c r="D15" s="72">
-        <v>133645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="72">
-        <v>54193</v>
-      </c>
-      <c r="C16" s="72">
-        <v>53934</v>
-      </c>
-      <c r="D16" s="72">
-        <v>108127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="72">
-        <v>41572</v>
-      </c>
-      <c r="C17" s="72">
-        <v>40329</v>
-      </c>
-      <c r="D17" s="72">
-        <v>81901</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="72">
-        <v>28133</v>
-      </c>
-      <c r="C18" s="72">
-        <v>26903</v>
-      </c>
-      <c r="D18" s="72">
-        <v>55037</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A19" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="72">
-        <v>14118</v>
-      </c>
-      <c r="C19" s="72">
-        <v>13785</v>
-      </c>
-      <c r="D19" s="72">
-        <v>27903</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="72">
-        <v>19220</v>
-      </c>
-      <c r="C20" s="72">
-        <v>20767</v>
-      </c>
-      <c r="D20" s="72">
-        <v>39988</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="A21" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.85">
-      <c r="B24" s="70"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EEF1C8E-D6B9-4367-97B0-BA0B367D0AD5}">
-  <dimension ref="A1:O10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="30" x14ac:dyDescent="0.85"/>
-  <cols>
-    <col min="1" max="1" width="24" style="29" customWidth="1"/>
-    <col min="2" max="2" width="32.33203125" style="69" customWidth="1"/>
-    <col min="3" max="4" width="31.6640625" style="69" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="29"/>
-    <col min="6" max="8" width="15.6640625" style="29" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="11.5546875" style="29"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A1" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-    </row>
-    <row r="2" spans="1:15" ht="60" x14ac:dyDescent="0.85">
-      <c r="A2" s="71" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="66" t="s">
-        <v>57</v>
-      </c>
-      <c r="C2" s="66" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="66" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" s="76" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="74">
-        <v>2375470</v>
-      </c>
-      <c r="C3" s="74">
-        <v>2552062</v>
-      </c>
-      <c r="D3" s="74">
-        <v>4927532</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A4" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="72">
-        <v>1031249</v>
-      </c>
-      <c r="C4" s="72">
-        <v>1015215</v>
-      </c>
-      <c r="D4" s="72">
-        <v>2046465</v>
-      </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A5" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="72">
-        <v>1241178</v>
-      </c>
-      <c r="C5" s="72">
-        <v>1435061</v>
-      </c>
-      <c r="D5" s="72">
-        <v>2676239</v>
-      </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" s="72">
-        <v>103043</v>
-      </c>
-      <c r="C6" s="72">
-        <v>101785</v>
-      </c>
-      <c r="D6" s="72">
-        <v>204828</v>
-      </c>
-      <c r="F6" s="77"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="A7" s="16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.85">
-      <c r="B10" s="70"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E12B744F-6F17-4891-BC34-B3B89A801878}">
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
-  <cols>
-    <col min="1" max="1" width="97.88671875" style="32" bestFit="1" customWidth="1"/>
-    <col min="2" max="8" width="16.44140625" style="32" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" style="32" customWidth="1"/>
-    <col min="10" max="10" width="21.5546875" style="32" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="32"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="81" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="39"/>
-    </row>
-    <row r="2" spans="1:8" ht="27" thickBot="1" x14ac:dyDescent="0.75">
-      <c r="A2" s="84"/>
-      <c r="B2" s="83">
-        <v>1977</v>
-      </c>
-      <c r="C2" s="83">
-        <v>1988</v>
-      </c>
-      <c r="D2" s="83">
-        <v>2000</v>
-      </c>
-      <c r="E2" s="83">
-        <v>2013</v>
-      </c>
-      <c r="F2" s="83">
-        <v>2015</v>
-      </c>
-      <c r="G2" s="83">
-        <v>2019</v>
-      </c>
-      <c r="H2" s="83">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="27" thickTop="1" x14ac:dyDescent="0.7">
-      <c r="A3" s="36" t="s">
-        <v>49</v>
-      </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35">
-        <v>6.3</v>
-      </c>
-      <c r="D3" s="35">
-        <v>5</v>
-      </c>
-      <c r="E3" s="35">
-        <v>4.3</v>
-      </c>
-      <c r="F3" s="35">
-        <v>3.84</v>
-      </c>
-      <c r="G3" s="35">
-        <v>5.2</v>
-      </c>
-      <c r="H3" s="60">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="29.4" x14ac:dyDescent="0.7">
-      <c r="A4" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="35">
-        <v>49</v>
-      </c>
-      <c r="C4" s="35">
-        <v>45.2</v>
-      </c>
-      <c r="D4" s="35">
-        <v>36</v>
-      </c>
-      <c r="E4" s="35">
-        <v>32</v>
-      </c>
-      <c r="F4" s="35">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="G4" s="35">
-        <v>35.5</v>
-      </c>
-      <c r="H4" s="60">
-        <v>32.200000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A5" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5" s="35">
-        <v>62.8</v>
-      </c>
-      <c r="G5" s="35"/>
-      <c r="H5" s="60">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A6" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="35"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="35">
-        <v>64.3</v>
-      </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="60">
-        <v>69.900000000000006</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A7" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B7" s="35">
-        <v>40</v>
-      </c>
-      <c r="C7" s="35">
-        <v>48</v>
-      </c>
-      <c r="D7" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="E7" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="35">
-        <v>63.5</v>
-      </c>
-      <c r="G7" s="35"/>
-      <c r="H7" s="60">
-        <v>68.900000000000006</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="52.8" x14ac:dyDescent="0.7">
-      <c r="A8" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35">
-        <v>2.93</v>
-      </c>
-      <c r="D8" s="35">
-        <v>2.4</v>
-      </c>
-      <c r="E8" s="35">
-        <v>2.77</v>
-      </c>
-      <c r="F8" s="35">
-        <v>2.77</v>
-      </c>
-      <c r="G8" s="35">
-        <v>2.77</v>
-      </c>
-      <c r="H8" s="60">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A9" s="36" t="s">
-        <v>110</v>
-      </c>
-      <c r="B9" s="35">
-        <v>16.190000000000001</v>
-      </c>
-      <c r="C9" s="35">
-        <v>17.7</v>
-      </c>
-      <c r="D9" s="35">
-        <v>17</v>
-      </c>
-      <c r="E9" s="35">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="F9" s="35">
-        <v>16</v>
-      </c>
-      <c r="G9" s="35">
-        <v>14.1</v>
-      </c>
-      <c r="H9" s="60">
-        <v>14.2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A10" s="36" t="s">
-        <v>111</v>
-      </c>
-      <c r="B10" s="35"/>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35">
-        <v>16.8</v>
-      </c>
-      <c r="F10" s="35">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="G10" s="35">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="H10" s="60">
-        <v>16.5232614249534</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A11" s="36" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="35"/>
-      <c r="C11" s="35"/>
-      <c r="D11" s="35"/>
-      <c r="E11" s="35">
-        <v>28.4</v>
-      </c>
-      <c r="F11" s="35">
-        <v>28.9</v>
-      </c>
-      <c r="G11" s="35">
-        <v>30.2</v>
-      </c>
-      <c r="H11" s="60">
-        <v>27.684428243840099</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A12" s="36" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="35">
-        <v>43.97</v>
-      </c>
-      <c r="C12" s="35">
-        <v>44.3</v>
-      </c>
-      <c r="D12" s="35">
-        <v>43.5</v>
-      </c>
-      <c r="E12" s="35">
-        <v>44.2</v>
-      </c>
-      <c r="F12" s="35">
-        <v>43.4</v>
-      </c>
-      <c r="G12" s="35">
-        <v>41.7</v>
-      </c>
-      <c r="H12" s="60">
-        <v>41.531227347348697</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A13" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="35">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="C13" s="35">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="D13" s="35">
-        <v>0.7944444444444444</v>
-      </c>
-      <c r="E13" s="35">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="F13" s="35">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="G13" s="35">
-        <v>19.8</v>
-      </c>
-      <c r="H13" s="60">
-        <v>19.961745925589099</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A14" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" s="35">
-        <v>50.2</v>
-      </c>
-      <c r="C14" s="35">
-        <v>49.6</v>
-      </c>
-      <c r="D14" s="35">
-        <v>50.9</v>
-      </c>
-      <c r="E14" s="35">
-        <v>50.2</v>
-      </c>
-      <c r="F14" s="35">
-        <v>50.9</v>
-      </c>
-      <c r="G14" s="35">
-        <v>50.7</v>
-      </c>
-      <c r="H14" s="60">
-        <v>52.117620361244697</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A15" s="36" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="35">
-        <v>3.8</v>
-      </c>
-      <c r="C15" s="35">
-        <v>4</v>
-      </c>
-      <c r="D15" s="35">
-        <v>3.6</v>
-      </c>
-      <c r="E15" s="35">
-        <v>3.8</v>
-      </c>
-      <c r="F15" s="35">
-        <v>3.7</v>
-      </c>
-      <c r="G15" s="35">
-        <v>3.6</v>
-      </c>
-      <c r="H15" s="60">
-        <v>4.1568131864506404</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="52.8" x14ac:dyDescent="0.7">
-      <c r="A16" s="36" t="s">
-        <v>117</v>
-      </c>
-      <c r="B16" s="35">
-        <v>44</v>
-      </c>
-      <c r="C16" s="35">
-        <v>45</v>
-      </c>
-      <c r="D16" s="35">
-        <v>48</v>
-      </c>
-      <c r="E16" s="35">
-        <v>46</v>
-      </c>
-      <c r="F16" s="35">
-        <v>47</v>
-      </c>
-      <c r="G16" s="35">
-        <v>48.5</v>
-      </c>
-      <c r="H16" s="60">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.7">
-      <c r="A17" s="33" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="49"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="51"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26305625-B393-4676-885C-66F897A4EF8D}">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="26.4" x14ac:dyDescent="0.7"/>
-  <cols>
-    <col min="1" max="1" width="28.5546875" style="32" customWidth="1"/>
-    <col min="2" max="3" width="17.5546875" style="40" customWidth="1"/>
-    <col min="4" max="5" width="17.5546875" style="32" customWidth="1"/>
-    <col min="6" max="16384" width="11.44140625" style="32"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" ht="28.95" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A1" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A2" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="42">
-        <v>2000</v>
-      </c>
-      <c r="C2" s="42">
-        <v>2013</v>
-      </c>
-      <c r="D2" s="42">
-        <v>2019</v>
-      </c>
-      <c r="E2" s="42">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A3" s="38" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="35">
-        <v>5</v>
-      </c>
-      <c r="C3" s="34">
-        <v>4.3</v>
-      </c>
-      <c r="D3" s="34">
-        <v>5.2</v>
-      </c>
-      <c r="E3" s="34">
-        <v>4.7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A4" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="34">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="C4" s="34">
-        <v>4.8</v>
-      </c>
-      <c r="D4" s="34">
-        <v>6.3</v>
-      </c>
-      <c r="E4" s="34">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A5" s="41" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="34">
-        <v>4.7</v>
-      </c>
-      <c r="C5" s="34">
-        <v>4.2</v>
-      </c>
-      <c r="D5" s="34">
-        <v>6.1</v>
-      </c>
-      <c r="E5" s="34">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A6" s="41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="34">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="C6" s="34">
-        <v>4.3</v>
-      </c>
-      <c r="D6" s="34">
-        <v>5.7</v>
-      </c>
-      <c r="E6" s="34">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A7" s="41" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="34">
-        <v>5.6</v>
-      </c>
-      <c r="C7" s="34">
-        <v>5</v>
-      </c>
-      <c r="D7" s="35">
-        <v>6</v>
-      </c>
-      <c r="E7" s="35">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A8" s="41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="34">
-        <v>4.8</v>
-      </c>
-      <c r="C8" s="34">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D8" s="35">
-        <v>6</v>
-      </c>
-      <c r="E8" s="35">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A9" s="41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="34">
-        <v>4.7</v>
-      </c>
-      <c r="C9" s="34">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D9" s="34">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E9" s="34">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A10" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="34">
-        <v>4.3</v>
-      </c>
-      <c r="C10" s="34">
-        <v>3.8</v>
-      </c>
-      <c r="D10" s="34">
-        <v>4.2</v>
-      </c>
-      <c r="E10" s="35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A11" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="35">
-        <v>5</v>
-      </c>
-      <c r="C11" s="34">
-        <v>3.9</v>
-      </c>
-      <c r="D11" s="34">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E11" s="34">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A12" s="41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="34">
-        <v>4.2</v>
-      </c>
-      <c r="C12" s="34">
-        <v>3.9</v>
-      </c>
-      <c r="D12" s="35">
-        <v>6</v>
-      </c>
-      <c r="E12" s="35">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A13" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="B13" s="34">
-        <v>6.5</v>
-      </c>
-      <c r="C13" s="34">
-        <v>5.9</v>
-      </c>
-      <c r="D13" s="34">
-        <v>6.5</v>
-      </c>
-      <c r="E13" s="34">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A14" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="34">
-        <v>4.3</v>
-      </c>
-      <c r="C14" s="34">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D14" s="34">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="E14" s="35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A15" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="34">
-        <v>3.7</v>
-      </c>
-      <c r="C15" s="34">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D15" s="34">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="E15" s="34">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A16" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="B16" s="34">
-        <v>4.8</v>
-      </c>
-      <c r="C16" s="34">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D16" s="34">
-        <v>3.9</v>
-      </c>
-      <c r="E16" s="34">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A17" s="79" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="35">
-        <v>4</v>
-      </c>
-      <c r="E17" s="34">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A18" s="79" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="34"/>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34">
-        <v>3.9</v>
-      </c>
-      <c r="E18" s="34">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A19" s="79" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34">
-        <v>3.8</v>
-      </c>
-      <c r="E19" s="34">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.7">
-      <c r="A20" s="78" t="s">
-        <v>82</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>